--- a/models/deepseek-v4-pro-0813/deepseek-v4-pro-0813-analysis.xlsx
+++ b/models/deepseek-v4-pro-0813/deepseek-v4-pro-0813-analysis.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R5bc0a857e8564abb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="R6457b712e04b40f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="Rc2ae3408402040da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="R07e3fea0333b4183"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,13 +14,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="8">
     <x:numFmt numFmtId="200" formatCode="0.##"/>
     <x:numFmt numFmtId="201" formatCode="0.0000"/>
     <x:numFmt numFmtId="202" formatCode="#,##0.####"/>
     <x:numFmt numFmtId="203" formatCode="0.000000"/>
+    <x:numFmt numFmtId="204" formatCode="0.0%"/>
+    <x:numFmt numFmtId="205" formatCode="0.000"/>
+    <x:numFmt numFmtId="206" formatCode="0.00%"/>
+    <x:numFmt numFmtId="207" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -41,8 +45,14 @@
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -62,6 +72,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8EEF5"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -99,7 +124,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="42">
+  <x:cellXfs count="55">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -172,10 +197,71 @@
     <x:xf numFmtId="203" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:dxfs count="2">
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFA32020"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE9E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFA32020"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE9E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
 </x:styleSheet>
 </file>
 
@@ -6301,7 +6387,1405 @@
       <x:c r="O132" s="30"/>
       <x:c r="P132" s="30"/>
     </x:row>
+    <x:row r="135" ht="23" customHeight="1">
+      <x:c r="A135" s="42" t="str">
+        <x:v>PD 带宽争用耗时评估</x:v>
+      </x:c>
+      <x:c r="B135" s="30"/>
+      <x:c r="C135" s="30"/>
+      <x:c r="D135" s="30"/>
+      <x:c r="E135" s="30"/>
+      <x:c r="F135" s="30"/>
+      <x:c r="G135" s="30"/>
+      <x:c r="H135" s="30"/>
+      <x:c r="I135" s="30"/>
+      <x:c r="J135" s="30"/>
+      <x:c r="K135" s="30"/>
+      <x:c r="L135" s="30"/>
+    </x:row>
+    <x:row r="136" ht="23" customHeight="1">
+      <x:c r="A136" s="30" t="str">
+        <x:v>Prefill 当前表参数；100 GB/s 为归一化示例。所列事件的带宽项，不等于完整 forward 耗时。</x:v>
+      </x:c>
+      <x:c r="B136" s="30"/>
+      <x:c r="C136" s="30"/>
+      <x:c r="D136" s="30"/>
+      <x:c r="E136" s="30"/>
+      <x:c r="F136" s="30"/>
+      <x:c r="G136" s="30"/>
+      <x:c r="H136" s="30"/>
+      <x:c r="I136" s="30"/>
+      <x:c r="J136" s="30"/>
+      <x:c r="K136" s="30"/>
+      <x:c r="L136" s="30"/>
+    </x:row>
+    <x:row r="137" ht="38" customHeight="1">
+      <x:c r="A137" s="45" t="str">
+        <x:v>带宽降幅</x:v>
+      </x:c>
+      <x:c r="B137" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="C137" s="45" t="str">
+        <x:v>争用覆盖率</x:v>
+      </x:c>
+      <x:c r="D137" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="E137" s="45" t="str">
+        <x:v>基线 forward ms</x:v>
+      </x:c>
+      <x:c r="F137" s="45" t="str">
+        <x:v>实测输入</x:v>
+      </x:c>
+      <x:c r="G137" s="45" t="str">
+        <x:v>默认带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="H137" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="I137" s="30"/>
+      <x:c r="J137" s="30"/>
+      <x:c r="K137" s="30"/>
+      <x:c r="L137" s="30"/>
+    </x:row>
+    <x:row r="138" ht="23" customHeight="1">
+      <x:c r="A138" s="30"/>
+      <x:c r="B138" s="47" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="C138" s="30"/>
+      <x:c r="D138" s="47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E138" s="30"/>
+      <x:c r="F138" s="48"/>
+      <x:c r="G138" s="30"/>
+      <x:c r="H138" s="48" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I138" s="30"/>
+      <x:c r="J138" s="30"/>
+      <x:c r="K138" s="30"/>
+      <x:c r="L138" s="30"/>
+    </x:row>
+    <x:row r="139" ht="38" customHeight="1">
+      <x:c r="A139" s="45" t="str">
+        <x:v>通信基线 ms</x:v>
+      </x:c>
+      <x:c r="B139" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="C139" s="45" t="str">
+        <x:v>通信争用后 ms</x:v>
+      </x:c>
+      <x:c r="D139" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="E139" s="45" t="str">
+        <x:v>forward 增量 ms</x:v>
+      </x:c>
+      <x:c r="F139" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="G139" s="45" t="str">
+        <x:v>forward 新耗时 ms</x:v>
+      </x:c>
+      <x:c r="H139" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="I139" s="45" t="str">
+        <x:v>forward 增幅</x:v>
+      </x:c>
+      <x:c r="J139" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="K139" s="45" t="str">
+        <x:v>输入状态</x:v>
+      </x:c>
+      <x:c r="L139" s="45" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="23" customHeight="1">
+      <x:c r="A140" s="49"/>
+      <x:c r="B140" s="49" t="n">
+        <x:f>SUM(G144:G169)</x:f>
+        <x:v>365.62731519999994</x:v>
+      </x:c>
+      <x:c r="C140" s="49"/>
+      <x:c r="D140" s="49" t="n">
+        <x:f>SUM(H144:H169)</x:f>
+        <x:v>406.2525724444444</x:v>
+      </x:c>
+      <x:c r="E140" s="49"/>
+      <x:c r="F140" s="49" t="n">
+        <x:f>SUM(K144:K169)</x:f>
+        <x:v>40.62525724444444</x:v>
+      </x:c>
+      <x:c r="G140" s="49"/>
+      <x:c r="H140" s="49" t="str">
+        <x:f>IF(AND(ISNUMBER($F$138),$F$138&gt;0,$F$138&gt;=SUMPRODUCT(G144:G169,J144:J169)),$F$138+F140,"")</x:f>
+      </x:c>
+      <x:c r="I140" s="49"/>
+      <x:c r="J140" s="50" t="str">
+        <x:f>IF(AND(ISNUMBER($F$138),$F$138&gt;0,$F$138&gt;=SUMPRODUCT(G144:G169,J144:J169)),F140/$F$138,"")</x:f>
+      </x:c>
+      <x:c r="K140" s="49"/>
+      <x:c r="L140" s="49" t="str">
+        <x:f>IF($F$138="","待填基线",IF(AND(ISNUMBER($F$138),$F$138&gt;0,$F$138&gt;=SUMPRODUCT(G144:G169,J144:J169)),"已填基线","基线/暴露不一致"))</x:f>
+        <x:v>待填基线</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="23" customHeight="1">
+      <x:c r="A141" s="30" t="str">
+        <x:v>共享比例=0 表示独立链路；暴露系数=0 表示增量完全隐藏。默认均为 1，降幅只作用于带宽项。</x:v>
+      </x:c>
+      <x:c r="B141" s="30"/>
+      <x:c r="C141" s="30"/>
+      <x:c r="D141" s="30"/>
+      <x:c r="E141" s="30"/>
+      <x:c r="F141" s="30"/>
+      <x:c r="G141" s="30"/>
+      <x:c r="H141" s="30"/>
+      <x:c r="I141" s="30"/>
+      <x:c r="J141" s="30"/>
+      <x:c r="K141" s="30"/>
+      <x:c r="L141" s="30"/>
+    </x:row>
+    <x:row r="142" ht="23" customHeight="1">
+      <x:c r="A142" s="30" t="str">
+        <x:v>P: AllToAllV + 4 B 计数 Ring；D: A3 BF16 MC2 FullMesh。每事件带宽按端点发送量定义。</x:v>
+      </x:c>
+      <x:c r="B142" s="30"/>
+      <x:c r="C142" s="30"/>
+      <x:c r="D142" s="30"/>
+      <x:c r="E142" s="30"/>
+      <x:c r="F142" s="30"/>
+      <x:c r="G142" s="30"/>
+      <x:c r="H142" s="30"/>
+      <x:c r="I142" s="30"/>
+      <x:c r="J142" s="30"/>
+      <x:c r="K142" s="30"/>
+      <x:c r="L142" s="30"/>
+    </x:row>
+    <x:row r="143" ht="38" customHeight="1">
+      <x:c r="A143" s="45" t="str">
+        <x:v>并行域</x:v>
+      </x:c>
+      <x:c r="B143" s="45" t="str">
+        <x:v>模块</x:v>
+      </x:c>
+      <x:c r="C143" s="45" t="str">
+        <x:v>通信事件</x:v>
+      </x:c>
+      <x:c r="D143" s="45" t="str">
+        <x:v>GB/Rank/Step</x:v>
+      </x:c>
+      <x:c r="E143" s="45" t="str">
+        <x:v>有效带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="F143" s="45" t="str">
+        <x:v>共享比例</x:v>
+      </x:c>
+      <x:c r="G143" s="45" t="str">
+        <x:v>基线带宽项 ms</x:v>
+      </x:c>
+      <x:c r="H143" s="45" t="str">
+        <x:v>争用后带宽项 ms</x:v>
+      </x:c>
+      <x:c r="I143" s="45" t="str">
+        <x:v>通信增量 ms</x:v>
+      </x:c>
+      <x:c r="J143" s="45" t="str">
+        <x:v>暴露系数</x:v>
+      </x:c>
+      <x:c r="K143" s="45" t="str">
+        <x:v>forward 增量 ms</x:v>
+      </x:c>
+      <x:c r="L143" s="45" t="str">
+        <x:v>公式口径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="23" customHeight="1">
+      <x:c r="A144" s="30" t="str">
+        <x:v>Embedding TP</x:v>
+      </x:c>
+      <x:c r="B144" s="30" t="str">
+        <x:v>Embedding</x:v>
+      </x:c>
+      <x:c r="C144" s="30" t="str">
+        <x:v>标准 TP 输出</x:v>
+      </x:c>
+      <x:c r="D144" s="34" t="n">
+        <x:f>(K107*2^20)/1e9</x:f>
+        <x:v>0.205520896</x:v>
+      </x:c>
+      <x:c r="E144" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F144" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G144" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E144),E144&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F144),F144&gt;=0,F144&lt;=1,ISNUMBER(J144),J144&gt;=0,J144&lt;=1),D144/E144*1000,NA())</x:f>
+        <x:v>2.0552089600000003</x:v>
+      </x:c>
+      <x:c r="H144" s="34" t="n">
+        <x:f>G144+I144</x:f>
+        <x:v>2.2835655111111115</x:v>
+      </x:c>
+      <x:c r="I144" s="34" t="n">
+        <x:f>G144*F144*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0.22835655111111114</x:v>
+      </x:c>
+      <x:c r="J144" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K144" s="34" t="n">
+        <x:f>I144*J144</x:f>
+        <x:v>0.22835655111111114</x:v>
+      </x:c>
+      <x:c r="L144" s="30" t="str">
+        <x:v>原通信行 107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="23" customHeight="1">
+      <x:c r="A145" s="30" t="str">
+        <x:v>Embedding TP</x:v>
+      </x:c>
+      <x:c r="B145" s="30" t="str">
+        <x:v>Embedding</x:v>
+      </x:c>
+      <x:c r="C145" s="30" t="str">
+        <x:v>Fine TP Token ID</x:v>
+      </x:c>
+      <x:c r="D145" s="34" t="n">
+        <x:f>(K108*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E145" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F145" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G145" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E145),E145&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F145),F145&gt;=0,F145&lt;=1,ISNUMBER(J145),J145&gt;=0,J145&lt;=1),D145/E145*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H145" s="34" t="n">
+        <x:f>G145+I145</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I145" s="34" t="n">
+        <x:f>G145*F145*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J145" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K145" s="34" t="n">
+        <x:f>I145*J145</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L145" s="30" t="str">
+        <x:v>原通信行 108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="23" customHeight="1">
+      <x:c r="A146" s="30" t="str">
+        <x:v>Embedding TP</x:v>
+      </x:c>
+      <x:c r="B146" s="30" t="str">
+        <x:v>Embedding</x:v>
+      </x:c>
+      <x:c r="C146" s="30" t="str">
+        <x:v>Fine TP Hidden</x:v>
+      </x:c>
+      <x:c r="D146" s="34" t="n">
+        <x:f>(K109*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E146" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F146" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G146" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E146),E146&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F146),F146&gt;=0,F146&lt;=1,ISNUMBER(J146),J146&gt;=0,J146&lt;=1),D146/E146*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H146" s="34" t="n">
+        <x:f>G146+I146</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I146" s="34" t="n">
+        <x:f>G146*F146*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J146" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K146" s="34" t="n">
+        <x:f>I146*J146</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L146" s="30" t="str">
+        <x:v>原通信行 109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="23" customHeight="1">
+      <x:c r="A147" s="30" t="str">
+        <x:v>DSA CP</x:v>
+      </x:c>
+      <x:c r="B147" s="30" t="str">
+        <x:v>Sparse Attention</x:v>
+      </x:c>
+      <x:c r="C147" s="30" t="str">
+        <x:v>Q/KV 投影输入</x:v>
+      </x:c>
+      <x:c r="D147" s="34" t="n">
+        <x:f>(K110*2^20)/1e9</x:f>
+        <x:v>6.268387328</x:v>
+      </x:c>
+      <x:c r="E147" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F147" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G147" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E147),E147&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F147),F147&gt;=0,F147&lt;=1,ISNUMBER(J147),J147&gt;=0,J147&lt;=1),D147/E147*1000,NA())</x:f>
+        <x:v>62.68387327999999</x:v>
+      </x:c>
+      <x:c r="H147" s="34" t="n">
+        <x:f>G147+I147</x:f>
+        <x:v>69.64874808888888</x:v>
+      </x:c>
+      <x:c r="I147" s="34" t="n">
+        <x:f>G147*F147*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>6.964874808888888</x:v>
+      </x:c>
+      <x:c r="J147" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K147" s="34" t="n">
+        <x:f>I147*J147</x:f>
+        <x:v>6.964874808888888</x:v>
+      </x:c>
+      <x:c r="L147" s="30" t="str">
+        <x:v>原通信行 110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="23" customHeight="1">
+      <x:c r="A148" s="30" t="str">
+        <x:v>DSA CP</x:v>
+      </x:c>
+      <x:c r="B148" s="30" t="str">
+        <x:v>Sparse Attention</x:v>
+      </x:c>
+      <x:c r="C148" s="30" t="str">
+        <x:v>恢复 TP Head Layout</x:v>
+      </x:c>
+      <x:c r="D148" s="34" t="n">
+        <x:f>(K111*2^20)/1e9</x:f>
+        <x:v>7.163871232</x:v>
+      </x:c>
+      <x:c r="E148" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F148" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G148" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E148),E148&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F148),F148&gt;=0,F148&lt;=1,ISNUMBER(J148),J148&gt;=0,J148&lt;=1),D148/E148*1000,NA())</x:f>
+        <x:v>71.63871232000001</x:v>
+      </x:c>
+      <x:c r="H148" s="34" t="n">
+        <x:f>G148+I148</x:f>
+        <x:v>79.59856924444446</x:v>
+      </x:c>
+      <x:c r="I148" s="34" t="n">
+        <x:f>G148*F148*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>7.959856924444447</x:v>
+      </x:c>
+      <x:c r="J148" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K148" s="34" t="n">
+        <x:f>I148*J148</x:f>
+        <x:v>7.959856924444447</x:v>
+      </x:c>
+      <x:c r="L148" s="30" t="str">
+        <x:v>原通信行 111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="23" customHeight="1">
+      <x:c r="A149" s="30" t="str">
+        <x:v>DSA CP</x:v>
+      </x:c>
+      <x:c r="B149" s="30" t="str">
+        <x:v>Indexer</x:v>
+      </x:c>
+      <x:c r="C149" s="30" t="str">
+        <x:v>Top-k Index</x:v>
+      </x:c>
+      <x:c r="D149" s="34" t="n">
+        <x:f>(K112*2^20)/1e9</x:f>
+        <x:v>0.88080384</x:v>
+      </x:c>
+      <x:c r="E149" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F149" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G149" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E149),E149&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F149),F149&gt;=0,F149&lt;=1,ISNUMBER(J149),J149&gt;=0,J149&lt;=1),D149/E149*1000,NA())</x:f>
+        <x:v>8.808038400000001</x:v>
+      </x:c>
+      <x:c r="H149" s="34" t="n">
+        <x:f>G149+I149</x:f>
+        <x:v>9.786709333333334</x:v>
+      </x:c>
+      <x:c r="I149" s="34" t="n">
+        <x:f>G149*F149*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0.9786709333333334</x:v>
+      </x:c>
+      <x:c r="J149" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K149" s="34" t="n">
+        <x:f>I149*J149</x:f>
+        <x:v>0.9786709333333334</x:v>
+      </x:c>
+      <x:c r="L149" s="30" t="str">
+        <x:v>原通信行 112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="23" customHeight="1">
+      <x:c r="A150" s="30" t="str">
+        <x:v>O Proj TP</x:v>
+      </x:c>
+      <x:c r="B150" s="30" t="str">
+        <x:v>Sparse Attention</x:v>
+      </x:c>
+      <x:c r="C150" s="30" t="str">
+        <x:v>DSA CP 关闭</x:v>
+      </x:c>
+      <x:c r="D150" s="34" t="n">
+        <x:f>(K113*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E150" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F150" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G150" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E150),E150&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F150),F150&gt;=0,F150&lt;=1,ISNUMBER(J150),J150&gt;=0,J150&lt;=1),D150/E150*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H150" s="34" t="n">
+        <x:f>G150+I150</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I150" s="34" t="n">
+        <x:f>G150*F150*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J150" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K150" s="34" t="n">
+        <x:f>I150*J150</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L150" s="30" t="str">
+        <x:v>原通信行 113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="23" customHeight="1">
+      <x:c r="A151" s="30" t="str">
+        <x:v>EP</x:v>
+      </x:c>
+      <x:c r="B151" s="30" t="str">
+        <x:v>Routed Experts</x:v>
+      </x:c>
+      <x:c r="C151" s="30" t="str">
+        <x:v>Dispatch Hidden</x:v>
+      </x:c>
+      <x:c r="D151" s="34" t="n">
+        <x:f>(K114*2^20)/1e9</x:f>
+        <x:v>4.701290496</x:v>
+      </x:c>
+      <x:c r="E151" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F151" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G151" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E151),E151&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F151),F151&gt;=0,F151&lt;=1,ISNUMBER(J151),J151&gt;=0,J151&lt;=1),D151/E151*1000,NA())</x:f>
+        <x:v>47.01290496000001</x:v>
+      </x:c>
+      <x:c r="H151" s="34" t="n">
+        <x:f>G151+I151</x:f>
+        <x:v>52.236561066666674</x:v>
+      </x:c>
+      <x:c r="I151" s="34" t="n">
+        <x:f>G151*F151*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>5.223656106666668</x:v>
+      </x:c>
+      <x:c r="J151" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K151" s="34" t="n">
+        <x:f>I151*J151</x:f>
+        <x:v>5.223656106666668</x:v>
+      </x:c>
+      <x:c r="L151" s="30" t="str">
+        <x:v>原通信行 114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="23" customHeight="1">
+      <x:c r="A152" s="30" t="str">
+        <x:v>EP</x:v>
+      </x:c>
+      <x:c r="B152" s="30" t="str">
+        <x:v>Routed Experts</x:v>
+      </x:c>
+      <x:c r="C152" s="30" t="str">
+        <x:v>Combine Hidden</x:v>
+      </x:c>
+      <x:c r="D152" s="34" t="n">
+        <x:f>(K115*2^20)/1e9</x:f>
+        <x:v>4.701290496</x:v>
+      </x:c>
+      <x:c r="E152" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F152" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G152" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E152),E152&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F152),F152&gt;=0,F152&lt;=1,ISNUMBER(J152),J152&gt;=0,J152&lt;=1),D152/E152*1000,NA())</x:f>
+        <x:v>47.01290496000001</x:v>
+      </x:c>
+      <x:c r="H152" s="34" t="n">
+        <x:f>G152+I152</x:f>
+        <x:v>52.236561066666674</x:v>
+      </x:c>
+      <x:c r="I152" s="34" t="n">
+        <x:f>G152*F152*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>5.223656106666668</x:v>
+      </x:c>
+      <x:c r="J152" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K152" s="34" t="n">
+        <x:f>I152*J152</x:f>
+        <x:v>5.223656106666668</x:v>
+      </x:c>
+      <x:c r="L152" s="30" t="str">
+        <x:v>原通信行 115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="23" customHeight="1">
+      <x:c r="A153" s="30" t="str">
+        <x:v>DP</x:v>
+      </x:c>
+      <x:c r="B153" s="30" t="str">
+        <x:v>MoE</x:v>
+      </x:c>
+      <x:c r="C153" s="30" t="str">
+        <x:v>Hidden 输入</x:v>
+      </x:c>
+      <x:c r="D153" s="34" t="n">
+        <x:f>(K116*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E153" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F153" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G153" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E153),E153&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F153),F153&gt;=0,F153&lt;=1,ISNUMBER(J153),J153&gt;=0,J153&lt;=1),D153/E153*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H153" s="34" t="n">
+        <x:f>G153+I153</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I153" s="34" t="n">
+        <x:f>G153*F153*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J153" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K153" s="34" t="n">
+        <x:f>I153*J153</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L153" s="30" t="str">
+        <x:v>原通信行 116</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="23" customHeight="1">
+      <x:c r="A154" s="30" t="str">
+        <x:v>DP</x:v>
+      </x:c>
+      <x:c r="B154" s="30" t="str">
+        <x:v>MoE Router</x:v>
+      </x:c>
+      <x:c r="C154" s="30" t="str">
+        <x:v>Router Logits</x:v>
+      </x:c>
+      <x:c r="D154" s="34" t="n">
+        <x:f>(K117*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E154" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F154" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G154" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E154),E154&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F154),F154&gt;=0,F154&lt;=1,ISNUMBER(J154),J154&gt;=0,J154&lt;=1),D154/E154*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H154" s="34" t="n">
+        <x:f>G154+I154</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I154" s="34" t="n">
+        <x:f>G154*F154*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J154" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K154" s="34" t="n">
+        <x:f>I154*J154</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L154" s="30" t="str">
+        <x:v>原通信行 117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="23" customHeight="1">
+      <x:c r="A155" s="30" t="str">
+        <x:v>DP</x:v>
+      </x:c>
+      <x:c r="B155" s="30" t="str">
+        <x:v>MoE</x:v>
+      </x:c>
+      <x:c r="C155" s="30" t="str">
+        <x:v>Routed Expert 输出</x:v>
+      </x:c>
+      <x:c r="D155" s="34" t="n">
+        <x:f>(K118*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E155" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F155" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G155" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E155),E155&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F155),F155&gt;=0,F155&lt;=1,ISNUMBER(J155),J155&gt;=0,J155&lt;=1),D155/E155*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H155" s="34" t="n">
+        <x:f>G155+I155</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I155" s="34" t="n">
+        <x:f>G155*F155*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J155" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K155" s="34" t="n">
+        <x:f>I155*J155</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L155" s="30" t="str">
+        <x:v>原通信行 118</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="23" customHeight="1">
+      <x:c r="A156" s="30" t="str">
+        <x:v>共享专家 TP</x:v>
+      </x:c>
+      <x:c r="B156" s="30" t="str">
+        <x:v>Shared Experts</x:v>
+      </x:c>
+      <x:c r="C156" s="30" t="str">
+        <x:v>SP 输入</x:v>
+      </x:c>
+      <x:c r="D156" s="34" t="n">
+        <x:f>(K119*2^20)/1e9</x:f>
+        <x:v>6.268387328</x:v>
+      </x:c>
+      <x:c r="E156" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F156" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G156" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E156),E156&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F156),F156&gt;=0,F156&lt;=1,ISNUMBER(J156),J156&gt;=0,J156&lt;=1),D156/E156*1000,NA())</x:f>
+        <x:v>62.68387327999999</x:v>
+      </x:c>
+      <x:c r="H156" s="34" t="n">
+        <x:f>G156+I156</x:f>
+        <x:v>69.64874808888888</x:v>
+      </x:c>
+      <x:c r="I156" s="34" t="n">
+        <x:f>G156*F156*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>6.964874808888888</x:v>
+      </x:c>
+      <x:c r="J156" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K156" s="34" t="n">
+        <x:f>I156*J156</x:f>
+        <x:v>6.964874808888888</x:v>
+      </x:c>
+      <x:c r="L156" s="30" t="str">
+        <x:v>原通信行 119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="23" customHeight="1">
+      <x:c r="A157" s="30" t="str">
+        <x:v>共享专家 TP</x:v>
+      </x:c>
+      <x:c r="B157" s="30" t="str">
+        <x:v>Shared Experts</x:v>
+      </x:c>
+      <x:c r="C157" s="30" t="str">
+        <x:v>SP 输出</x:v>
+      </x:c>
+      <x:c r="D157" s="34" t="n">
+        <x:f>(K120*2^20)/1e9</x:f>
+        <x:v>6.268387328</x:v>
+      </x:c>
+      <x:c r="E157" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F157" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G157" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E157),E157&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F157),F157&gt;=0,F157&lt;=1,ISNUMBER(J157),J157&gt;=0,J157&lt;=1),D157/E157*1000,NA())</x:f>
+        <x:v>62.68387327999999</x:v>
+      </x:c>
+      <x:c r="H157" s="34" t="n">
+        <x:f>G157+I157</x:f>
+        <x:v>69.64874808888888</x:v>
+      </x:c>
+      <x:c r="I157" s="34" t="n">
+        <x:f>G157*F157*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>6.964874808888888</x:v>
+      </x:c>
+      <x:c r="J157" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K157" s="34" t="n">
+        <x:f>I157*J157</x:f>
+        <x:v>6.964874808888888</x:v>
+      </x:c>
+      <x:c r="L157" s="30" t="str">
+        <x:v>原通信行 120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="23" customHeight="1">
+      <x:c r="A158" s="30" t="str">
+        <x:v>共享专家 TP</x:v>
+      </x:c>
+      <x:c r="B158" s="30" t="str">
+        <x:v>Shared Experts</x:v>
+      </x:c>
+      <x:c r="C158" s="30" t="str">
+        <x:v>非 SP 输出</x:v>
+      </x:c>
+      <x:c r="D158" s="34" t="n">
+        <x:f>(K121*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E158" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F158" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G158" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E158),E158&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F158),F158&gt;=0,F158&lt;=1,ISNUMBER(J158),J158&gt;=0,J158&lt;=1),D158/E158*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H158" s="34" t="n">
+        <x:f>G158+I158</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I158" s="34" t="n">
+        <x:f>G158*F158*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J158" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K158" s="34" t="n">
+        <x:f>I158*J158</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L158" s="30" t="str">
+        <x:v>原通信行 121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="23" customHeight="1">
+      <x:c r="A159" s="30" t="str">
+        <x:v>PCP</x:v>
+      </x:c>
+      <x:c r="B159" s="30" t="str">
+        <x:v>MoE</x:v>
+      </x:c>
+      <x:c r="C159" s="30" t="str">
+        <x:v>Hidden 输入</x:v>
+      </x:c>
+      <x:c r="D159" s="34" t="n">
+        <x:f>(K122*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E159" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F159" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G159" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E159),E159&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F159),F159&gt;=0,F159&lt;=1,ISNUMBER(J159),J159&gt;=0,J159&lt;=1),D159/E159*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H159" s="34" t="n">
+        <x:f>G159+I159</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I159" s="34" t="n">
+        <x:f>G159*F159*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J159" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K159" s="34" t="n">
+        <x:f>I159*J159</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L159" s="30" t="str">
+        <x:v>原通信行 122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="23" customHeight="1">
+      <x:c r="A160" s="30" t="str">
+        <x:v>PCP</x:v>
+      </x:c>
+      <x:c r="B160" s="30" t="str">
+        <x:v>MoE Router</x:v>
+      </x:c>
+      <x:c r="C160" s="30" t="str">
+        <x:v>Router Logits</x:v>
+      </x:c>
+      <x:c r="D160" s="34" t="n">
+        <x:f>(K123*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E160" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F160" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G160" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E160),E160&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F160),F160&gt;=0,F160&lt;=1,ISNUMBER(J160),J160&gt;=0,J160&lt;=1),D160/E160*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H160" s="34" t="n">
+        <x:f>G160+I160</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I160" s="34" t="n">
+        <x:f>G160*F160*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J160" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K160" s="34" t="n">
+        <x:f>I160*J160</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L160" s="30" t="str">
+        <x:v>原通信行 123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="23" customHeight="1">
+      <x:c r="A161" s="30" t="str">
+        <x:v>PCP</x:v>
+      </x:c>
+      <x:c r="B161" s="30" t="str">
+        <x:v>MoE</x:v>
+      </x:c>
+      <x:c r="C161" s="30" t="str">
+        <x:v>Routed Expert 输出</x:v>
+      </x:c>
+      <x:c r="D161" s="34" t="n">
+        <x:f>(K124*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E161" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F161" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G161" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E161),E161&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F161),F161&gt;=0,F161&lt;=1,ISNUMBER(J161),J161&gt;=0,J161&lt;=1),D161/E161*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H161" s="34" t="n">
+        <x:f>G161+I161</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I161" s="34" t="n">
+        <x:f>G161*F161*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J161" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K161" s="34" t="n">
+        <x:f>I161*J161</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L161" s="30" t="str">
+        <x:v>原通信行 124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="23" customHeight="1">
+      <x:c r="A162" s="30" t="str">
+        <x:v>PCP</x:v>
+      </x:c>
+      <x:c r="B162" s="30" t="str">
+        <x:v>Attention KV</x:v>
+      </x:c>
+      <x:c r="C162" s="30" t="str">
+        <x:v>KV Cache 写入前</x:v>
+      </x:c>
+      <x:c r="D162" s="34" t="n">
+        <x:f>(K125*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E162" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F162" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G162" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E162),E162&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F162),F162&gt;=0,F162&lt;=1,ISNUMBER(J162),J162&gt;=0,J162&lt;=1),D162/E162*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H162" s="34" t="n">
+        <x:f>G162+I162</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I162" s="34" t="n">
+        <x:f>G162*F162*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J162" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K162" s="34" t="n">
+        <x:f>I162*J162</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L162" s="30" t="str">
+        <x:v>原通信行 125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="23" customHeight="1">
+      <x:c r="A163" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B163" s="30" t="str">
+        <x:v>Model Output</x:v>
+      </x:c>
+      <x:c r="C163" s="30" t="str">
+        <x:v>Final Norm 后</x:v>
+      </x:c>
+      <x:c r="D163" s="34" t="n">
+        <x:f>(K126*2^20)/1e9</x:f>
+        <x:v>0.102760448</x:v>
+      </x:c>
+      <x:c r="E163" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F163" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G163" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E163),E163&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F163),F163&gt;=0,F163&lt;=1,ISNUMBER(J163),J163&gt;=0,J163&lt;=1),D163/E163*1000,NA())</x:f>
+        <x:v>1.0276044800000002</x:v>
+      </x:c>
+      <x:c r="H163" s="34" t="n">
+        <x:f>G163+I163</x:f>
+        <x:v>1.1417827555555558</x:v>
+      </x:c>
+      <x:c r="I163" s="34" t="n">
+        <x:f>G163*F163*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0.11417827555555557</x:v>
+      </x:c>
+      <x:c r="J163" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K163" s="34" t="n">
+        <x:f>I163*J163</x:f>
+        <x:v>0.11417827555555557</x:v>
+      </x:c>
+      <x:c r="L163" s="30" t="str">
+        <x:v>原通信行 126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="23" customHeight="1">
+      <x:c r="A164" s="30" t="str">
+        <x:v>LM Head TP</x:v>
+      </x:c>
+      <x:c r="B164" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C164" s="30" t="str">
+        <x:v>完整 Logits</x:v>
+      </x:c>
+      <x:c r="D164" s="34" t="n">
+        <x:f>(K127*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E164" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F164" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G164" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E164),E164&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F164),F164&gt;=0,F164&lt;=1,ISNUMBER(J164),J164&gt;=0,J164&lt;=1),D164/E164*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H164" s="34" t="n">
+        <x:f>G164+I164</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I164" s="34" t="n">
+        <x:f>G164*F164*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J164" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K164" s="34" t="n">
+        <x:f>I164*J164</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L164" s="30" t="str">
+        <x:v>原通信行 127</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="23" customHeight="1">
+      <x:c r="A165" s="30" t="str">
+        <x:v>LM Head TP</x:v>
+      </x:c>
+      <x:c r="B165" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C165" s="30" t="str">
+        <x:v>Reduce Sample</x:v>
+      </x:c>
+      <x:c r="D165" s="34" t="n">
+        <x:f>(K128*2^20)/1e9</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="E165" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F165" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G165" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E165),E165&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F165),F165&gt;=0,F165&lt;=1,ISNUMBER(J165),J165&gt;=0,J165&lt;=1),D165/E165*1000,NA())</x:f>
+        <x:v>0.01376256</x:v>
+      </x:c>
+      <x:c r="H165" s="34" t="n">
+        <x:f>G165+I165</x:f>
+        <x:v>0.015291733333333333</x:v>
+      </x:c>
+      <x:c r="I165" s="34" t="n">
+        <x:f>G165*F165*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0.0015291733333333336</x:v>
+      </x:c>
+      <x:c r="J165" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K165" s="34" t="n">
+        <x:f>I165*J165</x:f>
+        <x:v>0.0015291733333333336</x:v>
+      </x:c>
+      <x:c r="L165" s="30" t="str">
+        <x:v>原通信行 128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="23" customHeight="1">
+      <x:c r="A166" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B166" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C166" s="30" t="str">
+        <x:v>Hidden 输入</x:v>
+      </x:c>
+      <x:c r="D166" s="34" t="n">
+        <x:f>(K129*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E166" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F166" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G166" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E166),E166&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F166),F166&gt;=0,F166&lt;=1,ISNUMBER(J166),J166&gt;=0,J166&lt;=1),D166/E166*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H166" s="34" t="n">
+        <x:f>G166+I166</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I166" s="34" t="n">
+        <x:f>G166*F166*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J166" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K166" s="34" t="n">
+        <x:f>I166*J166</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L166" s="30" t="str">
+        <x:v>原通信行 129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="23" customHeight="1">
+      <x:c r="A167" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B167" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C167" s="30" t="str">
+        <x:v>完整 Logits</x:v>
+      </x:c>
+      <x:c r="D167" s="34" t="n">
+        <x:f>(K130*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E167" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F167" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G167" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E167),E167&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F167),F167&gt;=0,F167&lt;=1,ISNUMBER(J167),J167&gt;=0,J167&lt;=1),D167/E167*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H167" s="34" t="n">
+        <x:f>G167+I167</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I167" s="34" t="n">
+        <x:f>G167*F167*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J167" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K167" s="34" t="n">
+        <x:f>I167*J167</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L167" s="30" t="str">
+        <x:v>原通信行 130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" ht="23" customHeight="1">
+      <x:c r="A168" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B168" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C168" s="30" t="str">
+        <x:v>Reduce Sample</x:v>
+      </x:c>
+      <x:c r="D168" s="34" t="n">
+        <x:f>(K131*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E168" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F168" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G168" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E168),E168&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F168),F168&gt;=0,F168&lt;=1,ISNUMBER(J168),J168&gt;=0,J168&lt;=1),D168/E168*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H168" s="34" t="n">
+        <x:f>G168+I168</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I168" s="34" t="n">
+        <x:f>G168*F168*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J168" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K168" s="34" t="n">
+        <x:f>I168*J168</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L168" s="30" t="str">
+        <x:v>原通信行 131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="23" customHeight="1">
+      <x:c r="A169" s="30" t="str">
+        <x:v>EP</x:v>
+      </x:c>
+      <x:c r="B169" s="30" t="str">
+        <x:v>MoE 计数</x:v>
+      </x:c>
+      <x:c r="C169" s="30" t="str">
+        <x:v>直方图 Ring AG</x:v>
+      </x:c>
+      <x:c r="D169" s="34" t="n">
+        <x:f>(IF(E114=0,0,H114*ROUNDUP(384/G114,0)*G114*4*(G114-1)))/1e9</x:f>
+        <x:v>0.000655872</x:v>
+      </x:c>
+      <x:c r="E169" s="51" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F169" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G169" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E169),E169&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F169),F169&gt;=0,F169&lt;=1,ISNUMBER(J169),J169&gt;=0,J169&lt;=1),D169/E169*1000,NA())</x:f>
+        <x:v>0.0065587200000000005</x:v>
+      </x:c>
+      <x:c r="H169" s="34" t="n">
+        <x:f>G169+I169</x:f>
+        <x:v>0.0072874666666666674</x:v>
+      </x:c>
+      <x:c r="I169" s="34" t="n">
+        <x:f>G169*F169*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0.0007287466666666667</x:v>
+      </x:c>
+      <x:c r="J169" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K169" s="34" t="n">
+        <x:f>I169*J169</x:f>
+        <x:v>0.0007287466666666667</x:v>
+      </x:c>
+      <x:c r="L169" s="30" t="str">
+        <x:v>额外控制量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="23" customHeight="1">
+      <x:c r="A170" s="53" t="str">
+        <x:v>所列事件串行相加</x:v>
+      </x:c>
+      <x:c r="B170" s="53"/>
+      <x:c r="C170" s="53"/>
+      <x:c r="D170" s="54" t="n">
+        <x:f>SUM(D144:D169)</x:f>
+        <x:v>36.56273152</x:v>
+      </x:c>
+      <x:c r="E170" s="54"/>
+      <x:c r="F170" s="53"/>
+      <x:c r="G170" s="54" t="n">
+        <x:f>SUM(G144:G169)</x:f>
+        <x:v>365.62731519999994</x:v>
+      </x:c>
+      <x:c r="H170" s="54" t="n">
+        <x:f>SUM(H144:H169)</x:f>
+        <x:v>406.2525724444444</x:v>
+      </x:c>
+      <x:c r="I170" s="54" t="n">
+        <x:f>SUM(I144:I169)</x:f>
+        <x:v>40.62525724444444</x:v>
+      </x:c>
+      <x:c r="J170" s="53"/>
+      <x:c r="K170" s="54" t="n">
+        <x:f>SUM(K144:K169)</x:f>
+        <x:v>40.62525724444444</x:v>
+      </x:c>
+      <x:c r="L170" s="53"/>
+    </x:row>
   </x:sheetData>
+  <x:conditionalFormatting sqref="L140:L140">
+    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="不一致"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -12033,7 +13517,1229 @@
       <x:c r="O128" s="30"/>
       <x:c r="P128" s="30"/>
     </x:row>
+    <x:row r="131" ht="23" customHeight="1">
+      <x:c r="A131" s="42" t="str">
+        <x:v>PD 带宽争用耗时评估</x:v>
+      </x:c>
+      <x:c r="B131" s="30"/>
+      <x:c r="C131" s="30"/>
+      <x:c r="D131" s="30"/>
+      <x:c r="E131" s="30"/>
+      <x:c r="F131" s="30"/>
+      <x:c r="G131" s="30"/>
+      <x:c r="H131" s="30"/>
+      <x:c r="I131" s="30"/>
+      <x:c r="J131" s="30"/>
+      <x:c r="K131" s="30"/>
+      <x:c r="L131" s="30"/>
+    </x:row>
+    <x:row r="132" ht="23" customHeight="1">
+      <x:c r="A132" s="30" t="str">
+        <x:v>Decode 当前表参数；100 GB/s 为归一化示例。所列事件的带宽项，不等于完整 forward 耗时。</x:v>
+      </x:c>
+      <x:c r="B132" s="30"/>
+      <x:c r="C132" s="30"/>
+      <x:c r="D132" s="30"/>
+      <x:c r="E132" s="30"/>
+      <x:c r="F132" s="30"/>
+      <x:c r="G132" s="30"/>
+      <x:c r="H132" s="30"/>
+      <x:c r="I132" s="30"/>
+      <x:c r="J132" s="30"/>
+      <x:c r="K132" s="30"/>
+      <x:c r="L132" s="30"/>
+    </x:row>
+    <x:row r="133" ht="38" customHeight="1">
+      <x:c r="A133" s="45" t="str">
+        <x:v>带宽降幅</x:v>
+      </x:c>
+      <x:c r="B133" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="C133" s="45" t="str">
+        <x:v>争用覆盖率</x:v>
+      </x:c>
+      <x:c r="D133" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="E133" s="45" t="str">
+        <x:v>基线 forward ms</x:v>
+      </x:c>
+      <x:c r="F133" s="45" t="str">
+        <x:v>实测输入</x:v>
+      </x:c>
+      <x:c r="G133" s="45" t="str">
+        <x:v>默认带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="H133" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="I133" s="30"/>
+      <x:c r="J133" s="30"/>
+      <x:c r="K133" s="30"/>
+      <x:c r="L133" s="30"/>
+    </x:row>
+    <x:row r="134" ht="23" customHeight="1">
+      <x:c r="A134" s="30"/>
+      <x:c r="B134" s="47" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="C134" s="30"/>
+      <x:c r="D134" s="47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E134" s="30"/>
+      <x:c r="F134" s="48"/>
+      <x:c r="G134" s="30"/>
+      <x:c r="H134" s="48" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I134" s="30"/>
+      <x:c r="J134" s="30"/>
+      <x:c r="K134" s="30"/>
+      <x:c r="L134" s="30"/>
+    </x:row>
+    <x:row r="135" ht="38" customHeight="1">
+      <x:c r="A135" s="45" t="str">
+        <x:v>通信基线 ms</x:v>
+      </x:c>
+      <x:c r="B135" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="C135" s="45" t="str">
+        <x:v>通信争用后 ms</x:v>
+      </x:c>
+      <x:c r="D135" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="E135" s="45" t="str">
+        <x:v>forward 增量 ms</x:v>
+      </x:c>
+      <x:c r="F135" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="G135" s="45" t="str">
+        <x:v>forward 新耗时 ms</x:v>
+      </x:c>
+      <x:c r="H135" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="I135" s="45" t="str">
+        <x:v>forward 增幅</x:v>
+      </x:c>
+      <x:c r="J135" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="K135" s="45" t="str">
+        <x:v>输入状态</x:v>
+      </x:c>
+      <x:c r="L135" s="45" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="23" customHeight="1">
+      <x:c r="A136" s="49"/>
+      <x:c r="B136" s="49" t="n">
+        <x:f>SUM(G140:G161)</x:f>
+        <x:v>46.250408959999994</x:v>
+      </x:c>
+      <x:c r="C136" s="49"/>
+      <x:c r="D136" s="49" t="n">
+        <x:f>SUM(H140:H161)</x:f>
+        <x:v>51.38934328888889</x:v>
+      </x:c>
+      <x:c r="E136" s="49"/>
+      <x:c r="F136" s="49" t="n">
+        <x:f>SUM(K140:K161)</x:f>
+        <x:v>5.1389343288888885</x:v>
+      </x:c>
+      <x:c r="G136" s="49"/>
+      <x:c r="H136" s="49" t="str">
+        <x:f>IF(AND(ISNUMBER($F$134),$F$134&gt;0,$F$134&gt;=SUMPRODUCT(G140:G161,J140:J161)),$F$134+F136,"")</x:f>
+      </x:c>
+      <x:c r="I136" s="49"/>
+      <x:c r="J136" s="50" t="str">
+        <x:f>IF(AND(ISNUMBER($F$134),$F$134&gt;0,$F$134&gt;=SUMPRODUCT(G140:G161,J140:J161)),F136/$F$134,"")</x:f>
+      </x:c>
+      <x:c r="K136" s="49"/>
+      <x:c r="L136" s="49" t="str">
+        <x:f>IF($F$134="","待填基线",IF(AND(ISNUMBER($F$134),$F$134&gt;0,$F$134&gt;=SUMPRODUCT(G140:G161,J140:J161)),"已填基线","基线/暴露不一致"))</x:f>
+        <x:v>待填基线</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="23" customHeight="1">
+      <x:c r="A137" s="30" t="str">
+        <x:v>共享比例=0 表示独立链路；暴露系数=0 表示增量完全隐藏。默认均为 1，降幅只作用于带宽项。</x:v>
+      </x:c>
+      <x:c r="B137" s="30"/>
+      <x:c r="C137" s="30"/>
+      <x:c r="D137" s="30"/>
+      <x:c r="E137" s="30"/>
+      <x:c r="F137" s="30"/>
+      <x:c r="G137" s="30"/>
+      <x:c r="H137" s="30"/>
+      <x:c r="I137" s="30"/>
+      <x:c r="J137" s="30"/>
+      <x:c r="K137" s="30"/>
+      <x:c r="L137" s="30"/>
+    </x:row>
+    <x:row r="138" ht="23" customHeight="1">
+      <x:c r="A138" s="30" t="str">
+        <x:v>P: AllToAllV + 4 B 计数 Ring；D: A3 BF16 MC2 FullMesh。每事件带宽按端点发送量定义。</x:v>
+      </x:c>
+      <x:c r="B138" s="30"/>
+      <x:c r="C138" s="30"/>
+      <x:c r="D138" s="30"/>
+      <x:c r="E138" s="30"/>
+      <x:c r="F138" s="30"/>
+      <x:c r="G138" s="30"/>
+      <x:c r="H138" s="30"/>
+      <x:c r="I138" s="30"/>
+      <x:c r="J138" s="30"/>
+      <x:c r="K138" s="30"/>
+      <x:c r="L138" s="30"/>
+    </x:row>
+    <x:row r="139" ht="38" customHeight="1">
+      <x:c r="A139" s="45" t="str">
+        <x:v>并行域</x:v>
+      </x:c>
+      <x:c r="B139" s="45" t="str">
+        <x:v>模块</x:v>
+      </x:c>
+      <x:c r="C139" s="45" t="str">
+        <x:v>通信事件</x:v>
+      </x:c>
+      <x:c r="D139" s="45" t="str">
+        <x:v>GB/Rank/Step</x:v>
+      </x:c>
+      <x:c r="E139" s="45" t="str">
+        <x:v>有效带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="F139" s="45" t="str">
+        <x:v>共享比例</x:v>
+      </x:c>
+      <x:c r="G139" s="45" t="str">
+        <x:v>基线带宽项 ms</x:v>
+      </x:c>
+      <x:c r="H139" s="45" t="str">
+        <x:v>争用后带宽项 ms</x:v>
+      </x:c>
+      <x:c r="I139" s="45" t="str">
+        <x:v>通信增量 ms</x:v>
+      </x:c>
+      <x:c r="J139" s="45" t="str">
+        <x:v>暴露系数</x:v>
+      </x:c>
+      <x:c r="K139" s="45" t="str">
+        <x:v>forward 增量 ms</x:v>
+      </x:c>
+      <x:c r="L139" s="45" t="str">
+        <x:v>公式口径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="23" customHeight="1">
+      <x:c r="A140" s="30" t="str">
+        <x:v>Embedding TP</x:v>
+      </x:c>
+      <x:c r="B140" s="30" t="str">
+        <x:v>Embedding</x:v>
+      </x:c>
+      <x:c r="C140" s="30" t="str">
+        <x:v>标准 TP 输出</x:v>
+      </x:c>
+      <x:c r="D140" s="34" t="n">
+        <x:f>(K107*2^20)/1e9</x:f>
+        <x:v>0.025690112</x:v>
+      </x:c>
+      <x:c r="E140" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F140" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G140" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E140),E140&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F140),F140&gt;=0,F140&lt;=1,ISNUMBER(J140),J140&gt;=0,J140&lt;=1),D140/E140*1000,NA())</x:f>
+        <x:v>0.25690112000000004</x:v>
+      </x:c>
+      <x:c r="H140" s="34" t="n">
+        <x:f>G140+I140</x:f>
+        <x:v>0.28544568888888894</x:v>
+      </x:c>
+      <x:c r="I140" s="34" t="n">
+        <x:f>G140*F140*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0.028544568888888892</x:v>
+      </x:c>
+      <x:c r="J140" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K140" s="34" t="n">
+        <x:f>I140*J140</x:f>
+        <x:v>0.028544568888888892</x:v>
+      </x:c>
+      <x:c r="L140" s="30" t="str">
+        <x:v>原通信行 107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="23" customHeight="1">
+      <x:c r="A141" s="30" t="str">
+        <x:v>Embedding TP</x:v>
+      </x:c>
+      <x:c r="B141" s="30" t="str">
+        <x:v>Embedding</x:v>
+      </x:c>
+      <x:c r="C141" s="30" t="str">
+        <x:v>Fine TP Token ID</x:v>
+      </x:c>
+      <x:c r="D141" s="34" t="n">
+        <x:f>(K108*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E141" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F141" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G141" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E141),E141&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F141),F141&gt;=0,F141&lt;=1,ISNUMBER(J141),J141&gt;=0,J141&lt;=1),D141/E141*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H141" s="34" t="n">
+        <x:f>G141+I141</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I141" s="34" t="n">
+        <x:f>G141*F141*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J141" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K141" s="34" t="n">
+        <x:f>I141*J141</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L141" s="30" t="str">
+        <x:v>原通信行 108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" ht="23" customHeight="1">
+      <x:c r="A142" s="30" t="str">
+        <x:v>Embedding TP</x:v>
+      </x:c>
+      <x:c r="B142" s="30" t="str">
+        <x:v>Embedding</x:v>
+      </x:c>
+      <x:c r="C142" s="30" t="str">
+        <x:v>Fine TP Hidden</x:v>
+      </x:c>
+      <x:c r="D142" s="34" t="n">
+        <x:f>(K109*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E142" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F142" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G142" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E142),E142&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F142),F142&gt;=0,F142&lt;=1,ISNUMBER(J142),J142&gt;=0,J142&lt;=1),D142/E142*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H142" s="34" t="n">
+        <x:f>G142+I142</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I142" s="34" t="n">
+        <x:f>G142*F142*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J142" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K142" s="34" t="n">
+        <x:f>I142*J142</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L142" s="30" t="str">
+        <x:v>原通信行 109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="23" customHeight="1">
+      <x:c r="A143" s="30" t="str">
+        <x:v>DSA CP</x:v>
+      </x:c>
+      <x:c r="B143" s="30" t="str">
+        <x:v>Sparse Attention</x:v>
+      </x:c>
+      <x:c r="C143" s="30" t="str">
+        <x:v>Q/KV 投影输入</x:v>
+      </x:c>
+      <x:c r="D143" s="34" t="n">
+        <x:f>(K110*2^20)/1e9</x:f>
+        <x:v>0.783548416</x:v>
+      </x:c>
+      <x:c r="E143" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F143" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G143" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E143),E143&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F143),F143&gt;=0,F143&lt;=1,ISNUMBER(J143),J143&gt;=0,J143&lt;=1),D143/E143*1000,NA())</x:f>
+        <x:v>7.835484159999999</x:v>
+      </x:c>
+      <x:c r="H143" s="34" t="n">
+        <x:f>G143+I143</x:f>
+        <x:v>8.70609351111111</x:v>
+      </x:c>
+      <x:c r="I143" s="34" t="n">
+        <x:f>G143*F143*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0.870609351111111</x:v>
+      </x:c>
+      <x:c r="J143" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K143" s="34" t="n">
+        <x:f>I143*J143</x:f>
+        <x:v>0.870609351111111</x:v>
+      </x:c>
+      <x:c r="L143" s="30" t="str">
+        <x:v>原通信行 110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="23" customHeight="1">
+      <x:c r="A144" s="30" t="str">
+        <x:v>DSA CP</x:v>
+      </x:c>
+      <x:c r="B144" s="30" t="str">
+        <x:v>Sparse Attention</x:v>
+      </x:c>
+      <x:c r="C144" s="30" t="str">
+        <x:v>恢复 TP Head Layout</x:v>
+      </x:c>
+      <x:c r="D144" s="34" t="n">
+        <x:f>(K111*2^20)/1e9</x:f>
+        <x:v>0.895483904</x:v>
+      </x:c>
+      <x:c r="E144" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F144" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G144" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E144),E144&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F144),F144&gt;=0,F144&lt;=1,ISNUMBER(J144),J144&gt;=0,J144&lt;=1),D144/E144*1000,NA())</x:f>
+        <x:v>8.954839040000001</x:v>
+      </x:c>
+      <x:c r="H144" s="34" t="n">
+        <x:f>G144+I144</x:f>
+        <x:v>9.949821155555558</x:v>
+      </x:c>
+      <x:c r="I144" s="34" t="n">
+        <x:f>G144*F144*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0.9949821155555558</x:v>
+      </x:c>
+      <x:c r="J144" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K144" s="34" t="n">
+        <x:f>I144*J144</x:f>
+        <x:v>0.9949821155555558</x:v>
+      </x:c>
+      <x:c r="L144" s="30" t="str">
+        <x:v>原通信行 111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="23" customHeight="1">
+      <x:c r="A145" s="30" t="str">
+        <x:v>DSA CP</x:v>
+      </x:c>
+      <x:c r="B145" s="30" t="str">
+        <x:v>Indexer</x:v>
+      </x:c>
+      <x:c r="C145" s="30" t="str">
+        <x:v>Top-k Index</x:v>
+      </x:c>
+      <x:c r="D145" s="34" t="n">
+        <x:f>(K112*2^20)/1e9</x:f>
+        <x:v>0.11010048</x:v>
+      </x:c>
+      <x:c r="E145" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F145" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G145" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E145),E145&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F145),F145&gt;=0,F145&lt;=1,ISNUMBER(J145),J145&gt;=0,J145&lt;=1),D145/E145*1000,NA())</x:f>
+        <x:v>1.1010048000000001</x:v>
+      </x:c>
+      <x:c r="H145" s="34" t="n">
+        <x:f>G145+I145</x:f>
+        <x:v>1.2233386666666668</x:v>
+      </x:c>
+      <x:c r="I145" s="34" t="n">
+        <x:f>G145*F145*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0.12233386666666668</x:v>
+      </x:c>
+      <x:c r="J145" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K145" s="34" t="n">
+        <x:f>I145*J145</x:f>
+        <x:v>0.12233386666666668</x:v>
+      </x:c>
+      <x:c r="L145" s="30" t="str">
+        <x:v>原通信行 112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="23" customHeight="1">
+      <x:c r="A146" s="30" t="str">
+        <x:v>O Proj TP</x:v>
+      </x:c>
+      <x:c r="B146" s="30" t="str">
+        <x:v>Sparse Attention</x:v>
+      </x:c>
+      <x:c r="C146" s="30" t="str">
+        <x:v>DSA CP 关闭</x:v>
+      </x:c>
+      <x:c r="D146" s="34" t="n">
+        <x:f>(K113*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E146" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F146" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G146" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E146),E146&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F146),F146&gt;=0,F146&lt;=1,ISNUMBER(J146),J146&gt;=0,J146&lt;=1),D146/E146*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H146" s="34" t="n">
+        <x:f>G146+I146</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I146" s="34" t="n">
+        <x:f>G146*F146*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J146" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K146" s="34" t="n">
+        <x:f>I146*J146</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L146" s="30" t="str">
+        <x:v>原通信行 113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="23" customHeight="1">
+      <x:c r="A147" s="30" t="str">
+        <x:v>EP</x:v>
+      </x:c>
+      <x:c r="B147" s="30" t="str">
+        <x:v>Routed Experts</x:v>
+      </x:c>
+      <x:c r="C147" s="30" t="str">
+        <x:v>MC2 FullMesh Dispatch</x:v>
+      </x:c>
+      <x:c r="D147" s="34" t="n">
+        <x:f>(IF(F114=2,E114/7168*H114*(ROUNDUP((ROUNDUP(7168*F114/32,0)*32+32)/480,0)*512),NA()))/1e9</x:f>
+        <x:v>0.62963712</x:v>
+      </x:c>
+      <x:c r="E147" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F147" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G147" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E147),E147&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F147),F147&gt;=0,F147&lt;=1,ISNUMBER(J147),J147&gt;=0,J147&lt;=1),D147/E147*1000,NA())</x:f>
+        <x:v>6.2963712</x:v>
+      </x:c>
+      <x:c r="H147" s="34" t="n">
+        <x:f>G147+I147</x:f>
+        <x:v>6.995968</x:v>
+      </x:c>
+      <x:c r="I147" s="34" t="n">
+        <x:f>G147*F147*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0.6995968</x:v>
+      </x:c>
+      <x:c r="J147" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K147" s="34" t="n">
+        <x:f>I147*J147</x:f>
+        <x:v>0.6995968</x:v>
+      </x:c>
+      <x:c r="L147" s="30" t="str">
+        <x:v>原通信行 114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="23" customHeight="1">
+      <x:c r="A148" s="30" t="str">
+        <x:v>EP</x:v>
+      </x:c>
+      <x:c r="B148" s="30" t="str">
+        <x:v>Routed Experts</x:v>
+      </x:c>
+      <x:c r="C148" s="30" t="str">
+        <x:v>MC2 Combine + flags</x:v>
+      </x:c>
+      <x:c r="D148" s="34" t="n">
+        <x:f>(IF(F115=2,K115*2^20+E115/7168*H115*32,NA()))/1e9</x:f>
+        <x:v>0.588973056</x:v>
+      </x:c>
+      <x:c r="E148" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F148" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G148" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E148),E148&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F148),F148&gt;=0,F148&lt;=1,ISNUMBER(J148),J148&gt;=0,J148&lt;=1),D148/E148*1000,NA())</x:f>
+        <x:v>5.88973056</x:v>
+      </x:c>
+      <x:c r="H148" s="34" t="n">
+        <x:f>G148+I148</x:f>
+        <x:v>6.544145066666667</x:v>
+      </x:c>
+      <x:c r="I148" s="34" t="n">
+        <x:f>G148*F148*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0.6544145066666667</x:v>
+      </x:c>
+      <x:c r="J148" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K148" s="34" t="n">
+        <x:f>I148*J148</x:f>
+        <x:v>0.6544145066666667</x:v>
+      </x:c>
+      <x:c r="L148" s="30" t="str">
+        <x:v>原通信行 115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="23" customHeight="1">
+      <x:c r="A149" s="30" t="str">
+        <x:v>DP</x:v>
+      </x:c>
+      <x:c r="B149" s="30" t="str">
+        <x:v>MoE</x:v>
+      </x:c>
+      <x:c r="C149" s="30" t="str">
+        <x:v>Hidden 输入</x:v>
+      </x:c>
+      <x:c r="D149" s="34" t="n">
+        <x:f>(K116*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E149" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F149" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G149" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E149),E149&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F149),F149&gt;=0,F149&lt;=1,ISNUMBER(J149),J149&gt;=0,J149&lt;=1),D149/E149*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H149" s="34" t="n">
+        <x:f>G149+I149</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I149" s="34" t="n">
+        <x:f>G149*F149*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J149" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K149" s="34" t="n">
+        <x:f>I149*J149</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L149" s="30" t="str">
+        <x:v>原通信行 116</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="23" customHeight="1">
+      <x:c r="A150" s="30" t="str">
+        <x:v>DP</x:v>
+      </x:c>
+      <x:c r="B150" s="30" t="str">
+        <x:v>MoE Router</x:v>
+      </x:c>
+      <x:c r="C150" s="30" t="str">
+        <x:v>Router Logits</x:v>
+      </x:c>
+      <x:c r="D150" s="34" t="n">
+        <x:f>(K117*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E150" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F150" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G150" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E150),E150&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F150),F150&gt;=0,F150&lt;=1,ISNUMBER(J150),J150&gt;=0,J150&lt;=1),D150/E150*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H150" s="34" t="n">
+        <x:f>G150+I150</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I150" s="34" t="n">
+        <x:f>G150*F150*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J150" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K150" s="34" t="n">
+        <x:f>I150*J150</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L150" s="30" t="str">
+        <x:v>原通信行 117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="23" customHeight="1">
+      <x:c r="A151" s="30" t="str">
+        <x:v>DP</x:v>
+      </x:c>
+      <x:c r="B151" s="30" t="str">
+        <x:v>MoE</x:v>
+      </x:c>
+      <x:c r="C151" s="30" t="str">
+        <x:v>Routed Expert 输出</x:v>
+      </x:c>
+      <x:c r="D151" s="34" t="n">
+        <x:f>(K118*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E151" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F151" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G151" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E151),E151&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F151),F151&gt;=0,F151&lt;=1,ISNUMBER(J151),J151&gt;=0,J151&lt;=1),D151/E151*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H151" s="34" t="n">
+        <x:f>G151+I151</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I151" s="34" t="n">
+        <x:f>G151*F151*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J151" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K151" s="34" t="n">
+        <x:f>I151*J151</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L151" s="30" t="str">
+        <x:v>原通信行 118</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="23" customHeight="1">
+      <x:c r="A152" s="30" t="str">
+        <x:v>共享专家 TP</x:v>
+      </x:c>
+      <x:c r="B152" s="30" t="str">
+        <x:v>Shared Experts</x:v>
+      </x:c>
+      <x:c r="C152" s="30" t="str">
+        <x:v>SP 输入</x:v>
+      </x:c>
+      <x:c r="D152" s="34" t="n">
+        <x:f>(K119*2^20)/1e9</x:f>
+        <x:v>0.783548416</x:v>
+      </x:c>
+      <x:c r="E152" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F152" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G152" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E152),E152&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F152),F152&gt;=0,F152&lt;=1,ISNUMBER(J152),J152&gt;=0,J152&lt;=1),D152/E152*1000,NA())</x:f>
+        <x:v>7.835484159999999</x:v>
+      </x:c>
+      <x:c r="H152" s="34" t="n">
+        <x:f>G152+I152</x:f>
+        <x:v>8.70609351111111</x:v>
+      </x:c>
+      <x:c r="I152" s="34" t="n">
+        <x:f>G152*F152*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0.870609351111111</x:v>
+      </x:c>
+      <x:c r="J152" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K152" s="34" t="n">
+        <x:f>I152*J152</x:f>
+        <x:v>0.870609351111111</x:v>
+      </x:c>
+      <x:c r="L152" s="30" t="str">
+        <x:v>原通信行 119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="23" customHeight="1">
+      <x:c r="A153" s="30" t="str">
+        <x:v>共享专家 TP</x:v>
+      </x:c>
+      <x:c r="B153" s="30" t="str">
+        <x:v>Shared Experts</x:v>
+      </x:c>
+      <x:c r="C153" s="30" t="str">
+        <x:v>SP 输出</x:v>
+      </x:c>
+      <x:c r="D153" s="34" t="n">
+        <x:f>(K120*2^20)/1e9</x:f>
+        <x:v>0.783548416</x:v>
+      </x:c>
+      <x:c r="E153" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F153" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G153" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E153),E153&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F153),F153&gt;=0,F153&lt;=1,ISNUMBER(J153),J153&gt;=0,J153&lt;=1),D153/E153*1000,NA())</x:f>
+        <x:v>7.835484159999999</x:v>
+      </x:c>
+      <x:c r="H153" s="34" t="n">
+        <x:f>G153+I153</x:f>
+        <x:v>8.70609351111111</x:v>
+      </x:c>
+      <x:c r="I153" s="34" t="n">
+        <x:f>G153*F153*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0.870609351111111</x:v>
+      </x:c>
+      <x:c r="J153" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K153" s="34" t="n">
+        <x:f>I153*J153</x:f>
+        <x:v>0.870609351111111</x:v>
+      </x:c>
+      <x:c r="L153" s="30" t="str">
+        <x:v>原通信行 120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="23" customHeight="1">
+      <x:c r="A154" s="30" t="str">
+        <x:v>共享专家 TP</x:v>
+      </x:c>
+      <x:c r="B154" s="30" t="str">
+        <x:v>Shared Experts</x:v>
+      </x:c>
+      <x:c r="C154" s="30" t="str">
+        <x:v>非 SP 输出</x:v>
+      </x:c>
+      <x:c r="D154" s="34" t="n">
+        <x:f>(K121*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E154" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F154" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G154" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E154),E154&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F154),F154&gt;=0,F154&lt;=1,ISNUMBER(J154),J154&gt;=0,J154&lt;=1),D154/E154*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H154" s="34" t="n">
+        <x:f>G154+I154</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I154" s="34" t="n">
+        <x:f>G154*F154*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J154" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K154" s="34" t="n">
+        <x:f>I154*J154</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L154" s="30" t="str">
+        <x:v>原通信行 121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="23" customHeight="1">
+      <x:c r="A155" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B155" s="30" t="str">
+        <x:v>Model Output</x:v>
+      </x:c>
+      <x:c r="C155" s="30" t="str">
+        <x:v>Final Norm 后</x:v>
+      </x:c>
+      <x:c r="D155" s="34" t="n">
+        <x:f>(K122*2^20)/1e9</x:f>
+        <x:v>0.012845056</x:v>
+      </x:c>
+      <x:c r="E155" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F155" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G155" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E155),E155&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F155),F155&gt;=0,F155&lt;=1,ISNUMBER(J155),J155&gt;=0,J155&lt;=1),D155/E155*1000,NA())</x:f>
+        <x:v>0.12845056000000002</x:v>
+      </x:c>
+      <x:c r="H155" s="34" t="n">
+        <x:f>G155+I155</x:f>
+        <x:v>0.14272284444444447</x:v>
+      </x:c>
+      <x:c r="I155" s="34" t="n">
+        <x:f>G155*F155*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0.014272284444444446</x:v>
+      </x:c>
+      <x:c r="J155" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K155" s="34" t="n">
+        <x:f>I155*J155</x:f>
+        <x:v>0.014272284444444446</x:v>
+      </x:c>
+      <x:c r="L155" s="30" t="str">
+        <x:v>原通信行 122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="23" customHeight="1">
+      <x:c r="A156" s="30" t="str">
+        <x:v>LM Head TP</x:v>
+      </x:c>
+      <x:c r="B156" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C156" s="30" t="str">
+        <x:v>完整 Logits</x:v>
+      </x:c>
+      <x:c r="D156" s="34" t="n">
+        <x:f>(K123*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E156" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F156" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G156" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E156),E156&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F156),F156&gt;=0,F156&lt;=1,ISNUMBER(J156),J156&gt;=0,J156&lt;=1),D156/E156*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H156" s="34" t="n">
+        <x:f>G156+I156</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I156" s="34" t="n">
+        <x:f>G156*F156*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J156" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K156" s="34" t="n">
+        <x:f>I156*J156</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L156" s="30" t="str">
+        <x:v>原通信行 123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="23" customHeight="1">
+      <x:c r="A157" s="30" t="str">
+        <x:v>LM Head TP</x:v>
+      </x:c>
+      <x:c r="B157" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C157" s="30" t="str">
+        <x:v>Reduce Sample</x:v>
+      </x:c>
+      <x:c r="D157" s="34" t="n">
+        <x:f>(K124*2^20)/1e9</x:f>
+        <x:v>0.011010048</x:v>
+      </x:c>
+      <x:c r="E157" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F157" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G157" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E157),E157&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F157),F157&gt;=0,F157&lt;=1,ISNUMBER(J157),J157&gt;=0,J157&lt;=1),D157/E157*1000,NA())</x:f>
+        <x:v>0.11010048</x:v>
+      </x:c>
+      <x:c r="H157" s="34" t="n">
+        <x:f>G157+I157</x:f>
+        <x:v>0.12233386666666667</x:v>
+      </x:c>
+      <x:c r="I157" s="34" t="n">
+        <x:f>G157*F157*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0.012233386666666669</x:v>
+      </x:c>
+      <x:c r="J157" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K157" s="34" t="n">
+        <x:f>I157*J157</x:f>
+        <x:v>0.012233386666666669</x:v>
+      </x:c>
+      <x:c r="L157" s="30" t="str">
+        <x:v>原通信行 124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="23" customHeight="1">
+      <x:c r="A158" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B158" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C158" s="30" t="str">
+        <x:v>Hidden 输入</x:v>
+      </x:c>
+      <x:c r="D158" s="34" t="n">
+        <x:f>(K125*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E158" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F158" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G158" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E158),E158&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F158),F158&gt;=0,F158&lt;=1,ISNUMBER(J158),J158&gt;=0,J158&lt;=1),D158/E158*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H158" s="34" t="n">
+        <x:f>G158+I158</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I158" s="34" t="n">
+        <x:f>G158*F158*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J158" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K158" s="34" t="n">
+        <x:f>I158*J158</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L158" s="30" t="str">
+        <x:v>原通信行 125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="23" customHeight="1">
+      <x:c r="A159" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B159" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C159" s="30" t="str">
+        <x:v>完整 Logits</x:v>
+      </x:c>
+      <x:c r="D159" s="34" t="n">
+        <x:f>(K126*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E159" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F159" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G159" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E159),E159&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F159),F159&gt;=0,F159&lt;=1,ISNUMBER(J159),J159&gt;=0,J159&lt;=1),D159/E159*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H159" s="34" t="n">
+        <x:f>G159+I159</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I159" s="34" t="n">
+        <x:f>G159*F159*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J159" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K159" s="34" t="n">
+        <x:f>I159*J159</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L159" s="30" t="str">
+        <x:v>原通信行 126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="23" customHeight="1">
+      <x:c r="A160" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B160" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C160" s="30" t="str">
+        <x:v>Reduce Sample</x:v>
+      </x:c>
+      <x:c r="D160" s="34" t="n">
+        <x:f>(K127*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E160" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F160" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G160" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E160),E160&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F160),F160&gt;=0,F160&lt;=1,ISNUMBER(J160),J160&gt;=0,J160&lt;=1),D160/E160*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H160" s="34" t="n">
+        <x:f>G160+I160</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I160" s="34" t="n">
+        <x:f>G160*F160*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J160" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K160" s="34" t="n">
+        <x:f>I160*J160</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L160" s="30" t="str">
+        <x:v>原通信行 127</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="23" customHeight="1">
+      <x:c r="A161" s="30" t="str">
+        <x:v>EP</x:v>
+      </x:c>
+      <x:c r="B161" s="30" t="str">
+        <x:v>MoE 计数</x:v>
+      </x:c>
+      <x:c r="C161" s="30" t="str">
+        <x:v>MC2 count 写入</x:v>
+      </x:c>
+      <x:c r="D161" s="34" t="n">
+        <x:f>(IF(E114=0,0,H114*ROUNDUP(384/G114,0)*(G114-1)*32))/1e9</x:f>
+        <x:v>0.000655872</x:v>
+      </x:c>
+      <x:c r="E161" s="51" t="n">
+        <x:f>$H$134</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F161" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G161" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E161),E161&gt;0,ISNUMBER($B$134),$B$134&gt;=0,$B$134&lt;1,ISNUMBER($D$134),$D$134&gt;=0,$D$134&lt;=1,ISNUMBER(F161),F161&gt;=0,F161&lt;=1,ISNUMBER(J161),J161&gt;=0,J161&lt;=1),D161/E161*1000,NA())</x:f>
+        <x:v>0.0065587200000000005</x:v>
+      </x:c>
+      <x:c r="H161" s="34" t="n">
+        <x:f>G161+I161</x:f>
+        <x:v>0.0072874666666666674</x:v>
+      </x:c>
+      <x:c r="I161" s="34" t="n">
+        <x:f>G161*F161*$D$134*$B$134/(1-$B$134)</x:f>
+        <x:v>0.0007287466666666667</x:v>
+      </x:c>
+      <x:c r="J161" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K161" s="34" t="n">
+        <x:f>I161*J161</x:f>
+        <x:v>0.0007287466666666667</x:v>
+      </x:c>
+      <x:c r="L161" s="30" t="str">
+        <x:v>额外控制量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="23" customHeight="1">
+      <x:c r="A162" s="53" t="str">
+        <x:v>所列事件串行相加</x:v>
+      </x:c>
+      <x:c r="B162" s="53"/>
+      <x:c r="C162" s="53"/>
+      <x:c r="D162" s="54" t="n">
+        <x:f>SUM(D140:D161)</x:f>
+        <x:v>4.625040896000001</x:v>
+      </x:c>
+      <x:c r="E162" s="54"/>
+      <x:c r="F162" s="53"/>
+      <x:c r="G162" s="54" t="n">
+        <x:f>SUM(G140:G161)</x:f>
+        <x:v>46.250408959999994</x:v>
+      </x:c>
+      <x:c r="H162" s="54" t="n">
+        <x:f>SUM(H140:H161)</x:f>
+        <x:v>51.38934328888889</x:v>
+      </x:c>
+      <x:c r="I162" s="54" t="n">
+        <x:f>SUM(I140:I161)</x:f>
+        <x:v>5.1389343288888885</x:v>
+      </x:c>
+      <x:c r="J162" s="53"/>
+      <x:c r="K162" s="54" t="n">
+        <x:f>SUM(K140:K161)</x:f>
+        <x:v>5.1389343288888885</x:v>
+      </x:c>
+      <x:c r="L162" s="53"/>
+    </x:row>
   </x:sheetData>
+  <x:conditionalFormatting sqref="L136:L136">
+    <x:cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="不一致"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/models/deepseek-v4-pro-0813/deepseek-v4-pro-0813-analysis.xlsx
+++ b/models/deepseek-v4-pro-0813/deepseek-v4-pro-0813-analysis.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="Rc2ae3408402040da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="R07e3fea0333b4183"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R62b71513a46e4a73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="R7019aa64c1ce4cad"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -52,7 +52,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -87,6 +87,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8EEF5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -124,7 +129,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="55">
+  <x:cellXfs count="65">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -236,6 +241,36 @@
     <x:xf numFmtId="203" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -246,7 +281,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -256,7 +291,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -6387,8 +6422,8 @@
       <x:c r="O132" s="30"/>
       <x:c r="P132" s="30"/>
     </x:row>
-    <x:row r="135" ht="23" customHeight="1">
-      <x:c r="A135" s="42" t="str">
+    <x:row r="135" ht="15" customHeight="1">
+      <x:c r="A135" s="40" t="str">
         <x:v>PD 带宽争用耗时评估</x:v>
       </x:c>
       <x:c r="B135" s="30"/>
@@ -6403,7 +6438,7 @@
       <x:c r="K135" s="30"/>
       <x:c r="L135" s="30"/>
     </x:row>
-    <x:row r="136" ht="23" customHeight="1">
+    <x:row r="136" ht="15" customHeight="1">
       <x:c r="A136" s="30" t="str">
         <x:v>Prefill 当前表参数；100 GB/s 为归一化示例。所列事件的带宽项，不等于完整 forward 耗时。</x:v>
       </x:c>
@@ -6419,29 +6454,29 @@
       <x:c r="K136" s="30"/>
       <x:c r="L136" s="30"/>
     </x:row>
-    <x:row r="137" ht="38" customHeight="1">
-      <x:c r="A137" s="45" t="str">
+    <x:row r="137" ht="30" customHeight="1">
+      <x:c r="A137" s="62" t="str">
         <x:v>带宽降幅</x:v>
       </x:c>
-      <x:c r="B137" s="45" t="str">
+      <x:c r="B137" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
-      <x:c r="C137" s="45" t="str">
+      <x:c r="C137" s="62" t="str">
         <x:v>争用覆盖率</x:v>
       </x:c>
-      <x:c r="D137" s="45" t="str">
+      <x:c r="D137" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
-      <x:c r="E137" s="45" t="str">
+      <x:c r="E137" s="62" t="str">
         <x:v>基线 forward ms</x:v>
       </x:c>
-      <x:c r="F137" s="45" t="str">
+      <x:c r="F137" s="62" t="str">
         <x:v>实测输入</x:v>
       </x:c>
-      <x:c r="G137" s="45" t="str">
+      <x:c r="G137" s="62" t="str">
         <x:v>默认带宽 GB/s</x:v>
       </x:c>
-      <x:c r="H137" s="45" t="str">
+      <x:c r="H137" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
       <x:c r="I137" s="30"/>
@@ -6449,19 +6484,19 @@
       <x:c r="K137" s="30"/>
       <x:c r="L137" s="30"/>
     </x:row>
-    <x:row r="138" ht="23" customHeight="1">
+    <x:row r="138" ht="15" customHeight="1">
       <x:c r="A138" s="30"/>
-      <x:c r="B138" s="47" t="n">
+      <x:c r="B138" s="63" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C138" s="30"/>
-      <x:c r="D138" s="47" t="n">
+      <x:c r="D138" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E138" s="30"/>
-      <x:c r="F138" s="48"/>
+      <x:c r="F138" s="38"/>
       <x:c r="G138" s="30"/>
-      <x:c r="H138" s="48" t="n">
+      <x:c r="H138" s="36" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I138" s="30"/>
@@ -6469,45 +6504,45 @@
       <x:c r="K138" s="30"/>
       <x:c r="L138" s="30"/>
     </x:row>
-    <x:row r="139" ht="38" customHeight="1">
-      <x:c r="A139" s="45" t="str">
+    <x:row r="139" ht="30" customHeight="1">
+      <x:c r="A139" s="62" t="str">
         <x:v>通信基线 ms</x:v>
       </x:c>
-      <x:c r="B139" s="45" t="str">
+      <x:c r="B139" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="C139" s="45" t="str">
+      <x:c r="C139" s="62" t="str">
         <x:v>通信争用后 ms</x:v>
       </x:c>
-      <x:c r="D139" s="45" t="str">
+      <x:c r="D139" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="E139" s="45" t="str">
+      <x:c r="E139" s="62" t="str">
         <x:v>forward 增量 ms</x:v>
       </x:c>
-      <x:c r="F139" s="45" t="str">
+      <x:c r="F139" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="G139" s="45" t="str">
+      <x:c r="G139" s="62" t="str">
         <x:v>forward 新耗时 ms</x:v>
       </x:c>
-      <x:c r="H139" s="45" t="str">
+      <x:c r="H139" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="I139" s="45" t="str">
+      <x:c r="I139" s="62" t="str">
         <x:v>forward 增幅</x:v>
       </x:c>
-      <x:c r="J139" s="45" t="str">
+      <x:c r="J139" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="K139" s="45" t="str">
+      <x:c r="K139" s="62" t="str">
         <x:v>输入状态</x:v>
       </x:c>
-      <x:c r="L139" s="45" t="str">
+      <x:c r="L139" s="62" t="str">
         <x:v>状态</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" ht="23" customHeight="1">
+    <x:row r="140" ht="15" customHeight="1">
       <x:c r="A140" s="49"/>
       <x:c r="B140" s="49" t="n">
         <x:f>SUM(G144:G169)</x:f>
@@ -6537,7 +6572,7 @@
         <x:v>待填基线</x:v>
       </x:c>
     </x:row>
-    <x:row r="141" ht="23" customHeight="1">
+    <x:row r="141" ht="15" customHeight="1">
       <x:c r="A141" s="30" t="str">
         <x:v>共享比例=0 表示独立链路；暴露系数=0 表示增量完全隐藏。默认均为 1，降幅只作用于带宽项。</x:v>
       </x:c>
@@ -6553,7 +6588,7 @@
       <x:c r="K141" s="30"/>
       <x:c r="L141" s="30"/>
     </x:row>
-    <x:row r="142" ht="23" customHeight="1">
+    <x:row r="142" ht="15" customHeight="1">
       <x:c r="A142" s="30" t="str">
         <x:v>P: AllToAllV + 4 B 计数 Ring；D: A3 BF16 MC2 FullMesh。每事件带宽按端点发送量定义。</x:v>
       </x:c>
@@ -6569,45 +6604,45 @@
       <x:c r="K142" s="30"/>
       <x:c r="L142" s="30"/>
     </x:row>
-    <x:row r="143" ht="38" customHeight="1">
-      <x:c r="A143" s="45" t="str">
+    <x:row r="143" ht="30" customHeight="1">
+      <x:c r="A143" s="62" t="str">
         <x:v>并行域</x:v>
       </x:c>
-      <x:c r="B143" s="45" t="str">
+      <x:c r="B143" s="62" t="str">
         <x:v>模块</x:v>
       </x:c>
-      <x:c r="C143" s="45" t="str">
+      <x:c r="C143" s="62" t="str">
         <x:v>通信事件</x:v>
       </x:c>
-      <x:c r="D143" s="45" t="str">
+      <x:c r="D143" s="62" t="str">
         <x:v>GB/Rank/Step</x:v>
       </x:c>
-      <x:c r="E143" s="45" t="str">
+      <x:c r="E143" s="62" t="str">
         <x:v>有效带宽 GB/s</x:v>
       </x:c>
-      <x:c r="F143" s="45" t="str">
+      <x:c r="F143" s="62" t="str">
         <x:v>共享比例</x:v>
       </x:c>
-      <x:c r="G143" s="45" t="str">
+      <x:c r="G143" s="62" t="str">
         <x:v>基线带宽项 ms</x:v>
       </x:c>
-      <x:c r="H143" s="45" t="str">
+      <x:c r="H143" s="62" t="str">
         <x:v>争用后带宽项 ms</x:v>
       </x:c>
-      <x:c r="I143" s="45" t="str">
+      <x:c r="I143" s="62" t="str">
         <x:v>通信增量 ms</x:v>
       </x:c>
-      <x:c r="J143" s="45" t="str">
+      <x:c r="J143" s="62" t="str">
         <x:v>暴露系数</x:v>
       </x:c>
-      <x:c r="K143" s="45" t="str">
+      <x:c r="K143" s="62" t="str">
         <x:v>forward 增量 ms</x:v>
       </x:c>
-      <x:c r="L143" s="45" t="str">
+      <x:c r="L143" s="62" t="str">
         <x:v>公式口径</x:v>
       </x:c>
     </x:row>
-    <x:row r="144" ht="23" customHeight="1">
+    <x:row r="144" ht="15" customHeight="1">
       <x:c r="A144" s="30" t="str">
         <x:v>Embedding TP</x:v>
       </x:c>
@@ -6621,11 +6656,11 @@
         <x:f>(K107*2^20)/1e9</x:f>
         <x:v>0.205520896</x:v>
       </x:c>
-      <x:c r="E144" s="51" t="n">
+      <x:c r="E144" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F144" s="52" t="n">
+      <x:c r="F144" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G144" s="34" t="n">
@@ -6640,7 +6675,7 @@
         <x:f>G144*F144*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0.22835655111111114</x:v>
       </x:c>
-      <x:c r="J144" s="52" t="n">
+      <x:c r="J144" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K144" s="34" t="n">
@@ -6651,7 +6686,7 @@
         <x:v>原通信行 107</x:v>
       </x:c>
     </x:row>
-    <x:row r="145" ht="23" customHeight="1">
+    <x:row r="145" ht="15" customHeight="1">
       <x:c r="A145" s="30" t="str">
         <x:v>Embedding TP</x:v>
       </x:c>
@@ -6665,11 +6700,11 @@
         <x:f>(K108*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E145" s="51" t="n">
+      <x:c r="E145" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F145" s="52" t="n">
+      <x:c r="F145" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G145" s="34" t="n">
@@ -6684,7 +6719,7 @@
         <x:f>G145*F145*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J145" s="52" t="n">
+      <x:c r="J145" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K145" s="34" t="n">
@@ -6695,7 +6730,7 @@
         <x:v>原通信行 108</x:v>
       </x:c>
     </x:row>
-    <x:row r="146" ht="23" customHeight="1">
+    <x:row r="146" ht="15" customHeight="1">
       <x:c r="A146" s="30" t="str">
         <x:v>Embedding TP</x:v>
       </x:c>
@@ -6709,11 +6744,11 @@
         <x:f>(K109*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E146" s="51" t="n">
+      <x:c r="E146" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F146" s="52" t="n">
+      <x:c r="F146" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G146" s="34" t="n">
@@ -6728,7 +6763,7 @@
         <x:f>G146*F146*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J146" s="52" t="n">
+      <x:c r="J146" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K146" s="34" t="n">
@@ -6739,7 +6774,7 @@
         <x:v>原通信行 109</x:v>
       </x:c>
     </x:row>
-    <x:row r="147" ht="23" customHeight="1">
+    <x:row r="147" ht="15" customHeight="1">
       <x:c r="A147" s="30" t="str">
         <x:v>DSA CP</x:v>
       </x:c>
@@ -6753,11 +6788,11 @@
         <x:f>(K110*2^20)/1e9</x:f>
         <x:v>6.268387328</x:v>
       </x:c>
-      <x:c r="E147" s="51" t="n">
+      <x:c r="E147" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F147" s="52" t="n">
+      <x:c r="F147" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G147" s="34" t="n">
@@ -6772,7 +6807,7 @@
         <x:f>G147*F147*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>6.964874808888888</x:v>
       </x:c>
-      <x:c r="J147" s="52" t="n">
+      <x:c r="J147" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K147" s="34" t="n">
@@ -6783,7 +6818,7 @@
         <x:v>原通信行 110</x:v>
       </x:c>
     </x:row>
-    <x:row r="148" ht="23" customHeight="1">
+    <x:row r="148" ht="15" customHeight="1">
       <x:c r="A148" s="30" t="str">
         <x:v>DSA CP</x:v>
       </x:c>
@@ -6797,11 +6832,11 @@
         <x:f>(K111*2^20)/1e9</x:f>
         <x:v>7.163871232</x:v>
       </x:c>
-      <x:c r="E148" s="51" t="n">
+      <x:c r="E148" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F148" s="52" t="n">
+      <x:c r="F148" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G148" s="34" t="n">
@@ -6816,7 +6851,7 @@
         <x:f>G148*F148*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>7.959856924444447</x:v>
       </x:c>
-      <x:c r="J148" s="52" t="n">
+      <x:c r="J148" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K148" s="34" t="n">
@@ -6827,7 +6862,7 @@
         <x:v>原通信行 111</x:v>
       </x:c>
     </x:row>
-    <x:row r="149" ht="23" customHeight="1">
+    <x:row r="149" ht="15" customHeight="1">
       <x:c r="A149" s="30" t="str">
         <x:v>DSA CP</x:v>
       </x:c>
@@ -6841,11 +6876,11 @@
         <x:f>(K112*2^20)/1e9</x:f>
         <x:v>0.88080384</x:v>
       </x:c>
-      <x:c r="E149" s="51" t="n">
+      <x:c r="E149" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F149" s="52" t="n">
+      <x:c r="F149" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G149" s="34" t="n">
@@ -6860,7 +6895,7 @@
         <x:f>G149*F149*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0.9786709333333334</x:v>
       </x:c>
-      <x:c r="J149" s="52" t="n">
+      <x:c r="J149" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K149" s="34" t="n">
@@ -6871,7 +6906,7 @@
         <x:v>原通信行 112</x:v>
       </x:c>
     </x:row>
-    <x:row r="150" ht="23" customHeight="1">
+    <x:row r="150" ht="15" customHeight="1">
       <x:c r="A150" s="30" t="str">
         <x:v>O Proj TP</x:v>
       </x:c>
@@ -6885,11 +6920,11 @@
         <x:f>(K113*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E150" s="51" t="n">
+      <x:c r="E150" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F150" s="52" t="n">
+      <x:c r="F150" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G150" s="34" t="n">
@@ -6904,7 +6939,7 @@
         <x:f>G150*F150*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J150" s="52" t="n">
+      <x:c r="J150" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K150" s="34" t="n">
@@ -6915,7 +6950,7 @@
         <x:v>原通信行 113</x:v>
       </x:c>
     </x:row>
-    <x:row r="151" ht="23" customHeight="1">
+    <x:row r="151" ht="15" customHeight="1">
       <x:c r="A151" s="30" t="str">
         <x:v>EP</x:v>
       </x:c>
@@ -6929,11 +6964,11 @@
         <x:f>(K114*2^20)/1e9</x:f>
         <x:v>4.701290496</x:v>
       </x:c>
-      <x:c r="E151" s="51" t="n">
+      <x:c r="E151" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F151" s="52" t="n">
+      <x:c r="F151" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G151" s="34" t="n">
@@ -6948,7 +6983,7 @@
         <x:f>G151*F151*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>5.223656106666668</x:v>
       </x:c>
-      <x:c r="J151" s="52" t="n">
+      <x:c r="J151" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K151" s="34" t="n">
@@ -6959,7 +6994,7 @@
         <x:v>原通信行 114</x:v>
       </x:c>
     </x:row>
-    <x:row r="152" ht="23" customHeight="1">
+    <x:row r="152" ht="15" customHeight="1">
       <x:c r="A152" s="30" t="str">
         <x:v>EP</x:v>
       </x:c>
@@ -6973,11 +7008,11 @@
         <x:f>(K115*2^20)/1e9</x:f>
         <x:v>4.701290496</x:v>
       </x:c>
-      <x:c r="E152" s="51" t="n">
+      <x:c r="E152" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F152" s="52" t="n">
+      <x:c r="F152" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G152" s="34" t="n">
@@ -6992,7 +7027,7 @@
         <x:f>G152*F152*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>5.223656106666668</x:v>
       </x:c>
-      <x:c r="J152" s="52" t="n">
+      <x:c r="J152" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K152" s="34" t="n">
@@ -7003,7 +7038,7 @@
         <x:v>原通信行 115</x:v>
       </x:c>
     </x:row>
-    <x:row r="153" ht="23" customHeight="1">
+    <x:row r="153" ht="15" customHeight="1">
       <x:c r="A153" s="30" t="str">
         <x:v>DP</x:v>
       </x:c>
@@ -7017,11 +7052,11 @@
         <x:f>(K116*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E153" s="51" t="n">
+      <x:c r="E153" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F153" s="52" t="n">
+      <x:c r="F153" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G153" s="34" t="n">
@@ -7036,7 +7071,7 @@
         <x:f>G153*F153*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J153" s="52" t="n">
+      <x:c r="J153" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K153" s="34" t="n">
@@ -7047,7 +7082,7 @@
         <x:v>原通信行 116</x:v>
       </x:c>
     </x:row>
-    <x:row r="154" ht="23" customHeight="1">
+    <x:row r="154" ht="15" customHeight="1">
       <x:c r="A154" s="30" t="str">
         <x:v>DP</x:v>
       </x:c>
@@ -7061,11 +7096,11 @@
         <x:f>(K117*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E154" s="51" t="n">
+      <x:c r="E154" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F154" s="52" t="n">
+      <x:c r="F154" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G154" s="34" t="n">
@@ -7080,7 +7115,7 @@
         <x:f>G154*F154*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J154" s="52" t="n">
+      <x:c r="J154" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K154" s="34" t="n">
@@ -7091,7 +7126,7 @@
         <x:v>原通信行 117</x:v>
       </x:c>
     </x:row>
-    <x:row r="155" ht="23" customHeight="1">
+    <x:row r="155" ht="15" customHeight="1">
       <x:c r="A155" s="30" t="str">
         <x:v>DP</x:v>
       </x:c>
@@ -7105,11 +7140,11 @@
         <x:f>(K118*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E155" s="51" t="n">
+      <x:c r="E155" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F155" s="52" t="n">
+      <x:c r="F155" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G155" s="34" t="n">
@@ -7124,7 +7159,7 @@
         <x:f>G155*F155*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J155" s="52" t="n">
+      <x:c r="J155" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K155" s="34" t="n">
@@ -7135,7 +7170,7 @@
         <x:v>原通信行 118</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" ht="23" customHeight="1">
+    <x:row r="156" ht="15" customHeight="1">
       <x:c r="A156" s="30" t="str">
         <x:v>共享专家 TP</x:v>
       </x:c>
@@ -7149,11 +7184,11 @@
         <x:f>(K119*2^20)/1e9</x:f>
         <x:v>6.268387328</x:v>
       </x:c>
-      <x:c r="E156" s="51" t="n">
+      <x:c r="E156" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F156" s="52" t="n">
+      <x:c r="F156" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G156" s="34" t="n">
@@ -7168,7 +7203,7 @@
         <x:f>G156*F156*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>6.964874808888888</x:v>
       </x:c>
-      <x:c r="J156" s="52" t="n">
+      <x:c r="J156" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K156" s="34" t="n">
@@ -7179,7 +7214,7 @@
         <x:v>原通信行 119</x:v>
       </x:c>
     </x:row>
-    <x:row r="157" ht="23" customHeight="1">
+    <x:row r="157" ht="15" customHeight="1">
       <x:c r="A157" s="30" t="str">
         <x:v>共享专家 TP</x:v>
       </x:c>
@@ -7193,11 +7228,11 @@
         <x:f>(K120*2^20)/1e9</x:f>
         <x:v>6.268387328</x:v>
       </x:c>
-      <x:c r="E157" s="51" t="n">
+      <x:c r="E157" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F157" s="52" t="n">
+      <x:c r="F157" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G157" s="34" t="n">
@@ -7212,7 +7247,7 @@
         <x:f>G157*F157*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>6.964874808888888</x:v>
       </x:c>
-      <x:c r="J157" s="52" t="n">
+      <x:c r="J157" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K157" s="34" t="n">
@@ -7223,7 +7258,7 @@
         <x:v>原通信行 120</x:v>
       </x:c>
     </x:row>
-    <x:row r="158" ht="23" customHeight="1">
+    <x:row r="158" ht="15" customHeight="1">
       <x:c r="A158" s="30" t="str">
         <x:v>共享专家 TP</x:v>
       </x:c>
@@ -7237,11 +7272,11 @@
         <x:f>(K121*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E158" s="51" t="n">
+      <x:c r="E158" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F158" s="52" t="n">
+      <x:c r="F158" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G158" s="34" t="n">
@@ -7256,7 +7291,7 @@
         <x:f>G158*F158*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J158" s="52" t="n">
+      <x:c r="J158" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K158" s="34" t="n">
@@ -7267,7 +7302,7 @@
         <x:v>原通信行 121</x:v>
       </x:c>
     </x:row>
-    <x:row r="159" ht="23" customHeight="1">
+    <x:row r="159" ht="15" customHeight="1">
       <x:c r="A159" s="30" t="str">
         <x:v>PCP</x:v>
       </x:c>
@@ -7281,11 +7316,11 @@
         <x:f>(K122*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E159" s="51" t="n">
+      <x:c r="E159" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F159" s="52" t="n">
+      <x:c r="F159" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G159" s="34" t="n">
@@ -7300,7 +7335,7 @@
         <x:f>G159*F159*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J159" s="52" t="n">
+      <x:c r="J159" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K159" s="34" t="n">
@@ -7311,7 +7346,7 @@
         <x:v>原通信行 122</x:v>
       </x:c>
     </x:row>
-    <x:row r="160" ht="23" customHeight="1">
+    <x:row r="160" ht="15" customHeight="1">
       <x:c r="A160" s="30" t="str">
         <x:v>PCP</x:v>
       </x:c>
@@ -7325,11 +7360,11 @@
         <x:f>(K123*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E160" s="51" t="n">
+      <x:c r="E160" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F160" s="52" t="n">
+      <x:c r="F160" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G160" s="34" t="n">
@@ -7344,7 +7379,7 @@
         <x:f>G160*F160*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J160" s="52" t="n">
+      <x:c r="J160" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K160" s="34" t="n">
@@ -7355,7 +7390,7 @@
         <x:v>原通信行 123</x:v>
       </x:c>
     </x:row>
-    <x:row r="161" ht="23" customHeight="1">
+    <x:row r="161" ht="15" customHeight="1">
       <x:c r="A161" s="30" t="str">
         <x:v>PCP</x:v>
       </x:c>
@@ -7369,11 +7404,11 @@
         <x:f>(K124*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E161" s="51" t="n">
+      <x:c r="E161" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F161" s="52" t="n">
+      <x:c r="F161" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G161" s="34" t="n">
@@ -7388,7 +7423,7 @@
         <x:f>G161*F161*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J161" s="52" t="n">
+      <x:c r="J161" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K161" s="34" t="n">
@@ -7399,7 +7434,7 @@
         <x:v>原通信行 124</x:v>
       </x:c>
     </x:row>
-    <x:row r="162" ht="23" customHeight="1">
+    <x:row r="162" ht="15" customHeight="1">
       <x:c r="A162" s="30" t="str">
         <x:v>PCP</x:v>
       </x:c>
@@ -7413,11 +7448,11 @@
         <x:f>(K125*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E162" s="51" t="n">
+      <x:c r="E162" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F162" s="52" t="n">
+      <x:c r="F162" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G162" s="34" t="n">
@@ -7432,7 +7467,7 @@
         <x:f>G162*F162*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J162" s="52" t="n">
+      <x:c r="J162" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K162" s="34" t="n">
@@ -7443,7 +7478,7 @@
         <x:v>原通信行 125</x:v>
       </x:c>
     </x:row>
-    <x:row r="163" ht="23" customHeight="1">
+    <x:row r="163" ht="15" customHeight="1">
       <x:c r="A163" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -7457,11 +7492,11 @@
         <x:f>(K126*2^20)/1e9</x:f>
         <x:v>0.102760448</x:v>
       </x:c>
-      <x:c r="E163" s="51" t="n">
+      <x:c r="E163" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F163" s="52" t="n">
+      <x:c r="F163" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G163" s="34" t="n">
@@ -7476,7 +7511,7 @@
         <x:f>G163*F163*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0.11417827555555557</x:v>
       </x:c>
-      <x:c r="J163" s="52" t="n">
+      <x:c r="J163" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K163" s="34" t="n">
@@ -7487,7 +7522,7 @@
         <x:v>原通信行 126</x:v>
       </x:c>
     </x:row>
-    <x:row r="164" ht="23" customHeight="1">
+    <x:row r="164" ht="15" customHeight="1">
       <x:c r="A164" s="30" t="str">
         <x:v>LM Head TP</x:v>
       </x:c>
@@ -7501,11 +7536,11 @@
         <x:f>(K127*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E164" s="51" t="n">
+      <x:c r="E164" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F164" s="52" t="n">
+      <x:c r="F164" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G164" s="34" t="n">
@@ -7520,7 +7555,7 @@
         <x:f>G164*F164*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J164" s="52" t="n">
+      <x:c r="J164" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K164" s="34" t="n">
@@ -7531,7 +7566,7 @@
         <x:v>原通信行 127</x:v>
       </x:c>
     </x:row>
-    <x:row r="165" ht="23" customHeight="1">
+    <x:row r="165" ht="15" customHeight="1">
       <x:c r="A165" s="30" t="str">
         <x:v>LM Head TP</x:v>
       </x:c>
@@ -7545,11 +7580,11 @@
         <x:f>(K128*2^20)/1e9</x:f>
         <x:v>0.001376256</x:v>
       </x:c>
-      <x:c r="E165" s="51" t="n">
+      <x:c r="E165" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F165" s="52" t="n">
+      <x:c r="F165" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G165" s="34" t="n">
@@ -7564,7 +7599,7 @@
         <x:f>G165*F165*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0.0015291733333333336</x:v>
       </x:c>
-      <x:c r="J165" s="52" t="n">
+      <x:c r="J165" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K165" s="34" t="n">
@@ -7575,7 +7610,7 @@
         <x:v>原通信行 128</x:v>
       </x:c>
     </x:row>
-    <x:row r="166" ht="23" customHeight="1">
+    <x:row r="166" ht="15" customHeight="1">
       <x:c r="A166" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -7589,11 +7624,11 @@
         <x:f>(K129*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E166" s="51" t="n">
+      <x:c r="E166" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F166" s="52" t="n">
+      <x:c r="F166" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G166" s="34" t="n">
@@ -7608,7 +7643,7 @@
         <x:f>G166*F166*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J166" s="52" t="n">
+      <x:c r="J166" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K166" s="34" t="n">
@@ -7619,7 +7654,7 @@
         <x:v>原通信行 129</x:v>
       </x:c>
     </x:row>
-    <x:row r="167" ht="23" customHeight="1">
+    <x:row r="167" ht="15" customHeight="1">
       <x:c r="A167" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -7633,11 +7668,11 @@
         <x:f>(K130*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E167" s="51" t="n">
+      <x:c r="E167" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F167" s="52" t="n">
+      <x:c r="F167" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G167" s="34" t="n">
@@ -7652,7 +7687,7 @@
         <x:f>G167*F167*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J167" s="52" t="n">
+      <x:c r="J167" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K167" s="34" t="n">
@@ -7663,7 +7698,7 @@
         <x:v>原通信行 130</x:v>
       </x:c>
     </x:row>
-    <x:row r="168" ht="23" customHeight="1">
+    <x:row r="168" ht="15" customHeight="1">
       <x:c r="A168" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -7677,11 +7712,11 @@
         <x:f>(K131*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E168" s="51" t="n">
+      <x:c r="E168" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F168" s="52" t="n">
+      <x:c r="F168" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G168" s="34" t="n">
@@ -7696,7 +7731,7 @@
         <x:f>G168*F168*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J168" s="52" t="n">
+      <x:c r="J168" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K168" s="34" t="n">
@@ -7707,7 +7742,7 @@
         <x:v>原通信行 131</x:v>
       </x:c>
     </x:row>
-    <x:row r="169" ht="23" customHeight="1">
+    <x:row r="169" ht="15" customHeight="1">
       <x:c r="A169" s="30" t="str">
         <x:v>EP</x:v>
       </x:c>
@@ -7721,11 +7756,11 @@
         <x:f>(IF(E114=0,0,H114*ROUNDUP(384/G114,0)*G114*4*(G114-1)))/1e9</x:f>
         <x:v>0.000655872</x:v>
       </x:c>
-      <x:c r="E169" s="51" t="n">
+      <x:c r="E169" s="64" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F169" s="52" t="n">
+      <x:c r="F169" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G169" s="34" t="n">
@@ -7740,7 +7775,7 @@
         <x:f>G169*F169*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0.0007287466666666667</x:v>
       </x:c>
-      <x:c r="J169" s="52" t="n">
+      <x:c r="J169" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K169" s="34" t="n">
@@ -7751,36 +7786,36 @@
         <x:v>额外控制量</x:v>
       </x:c>
     </x:row>
-    <x:row r="170" ht="23" customHeight="1">
-      <x:c r="A170" s="53" t="str">
+    <x:row r="170" ht="15" customHeight="1">
+      <x:c r="A170" s="40" t="str">
         <x:v>所列事件串行相加</x:v>
       </x:c>
-      <x:c r="B170" s="53"/>
-      <x:c r="C170" s="53"/>
-      <x:c r="D170" s="54" t="n">
+      <x:c r="B170" s="40"/>
+      <x:c r="C170" s="40"/>
+      <x:c r="D170" s="41" t="n">
         <x:f>SUM(D144:D169)</x:f>
         <x:v>36.56273152</x:v>
       </x:c>
-      <x:c r="E170" s="54"/>
-      <x:c r="F170" s="53"/>
-      <x:c r="G170" s="54" t="n">
+      <x:c r="E170" s="40"/>
+      <x:c r="F170" s="40"/>
+      <x:c r="G170" s="41" t="n">
         <x:f>SUM(G144:G169)</x:f>
         <x:v>365.62731519999994</x:v>
       </x:c>
-      <x:c r="H170" s="54" t="n">
+      <x:c r="H170" s="41" t="n">
         <x:f>SUM(H144:H169)</x:f>
         <x:v>406.2525724444444</x:v>
       </x:c>
-      <x:c r="I170" s="54" t="n">
+      <x:c r="I170" s="41" t="n">
         <x:f>SUM(I144:I169)</x:f>
         <x:v>40.62525724444444</x:v>
       </x:c>
-      <x:c r="J170" s="53"/>
-      <x:c r="K170" s="54" t="n">
+      <x:c r="J170" s="40"/>
+      <x:c r="K170" s="41" t="n">
         <x:f>SUM(K144:K169)</x:f>
         <x:v>40.62525724444444</x:v>
       </x:c>
-      <x:c r="L170" s="53"/>
+      <x:c r="L170" s="40"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="L140:L140">
@@ -13517,8 +13552,8 @@
       <x:c r="O128" s="30"/>
       <x:c r="P128" s="30"/>
     </x:row>
-    <x:row r="131" ht="23" customHeight="1">
-      <x:c r="A131" s="42" t="str">
+    <x:row r="131" ht="15" customHeight="1">
+      <x:c r="A131" s="40" t="str">
         <x:v>PD 带宽争用耗时评估</x:v>
       </x:c>
       <x:c r="B131" s="30"/>
@@ -13533,7 +13568,7 @@
       <x:c r="K131" s="30"/>
       <x:c r="L131" s="30"/>
     </x:row>
-    <x:row r="132" ht="23" customHeight="1">
+    <x:row r="132" ht="15" customHeight="1">
       <x:c r="A132" s="30" t="str">
         <x:v>Decode 当前表参数；100 GB/s 为归一化示例。所列事件的带宽项，不等于完整 forward 耗时。</x:v>
       </x:c>
@@ -13549,29 +13584,29 @@
       <x:c r="K132" s="30"/>
       <x:c r="L132" s="30"/>
     </x:row>
-    <x:row r="133" ht="38" customHeight="1">
-      <x:c r="A133" s="45" t="str">
+    <x:row r="133" ht="30" customHeight="1">
+      <x:c r="A133" s="62" t="str">
         <x:v>带宽降幅</x:v>
       </x:c>
-      <x:c r="B133" s="45" t="str">
+      <x:c r="B133" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
-      <x:c r="C133" s="45" t="str">
+      <x:c r="C133" s="62" t="str">
         <x:v>争用覆盖率</x:v>
       </x:c>
-      <x:c r="D133" s="45" t="str">
+      <x:c r="D133" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
-      <x:c r="E133" s="45" t="str">
+      <x:c r="E133" s="62" t="str">
         <x:v>基线 forward ms</x:v>
       </x:c>
-      <x:c r="F133" s="45" t="str">
+      <x:c r="F133" s="62" t="str">
         <x:v>实测输入</x:v>
       </x:c>
-      <x:c r="G133" s="45" t="str">
+      <x:c r="G133" s="62" t="str">
         <x:v>默认带宽 GB/s</x:v>
       </x:c>
-      <x:c r="H133" s="45" t="str">
+      <x:c r="H133" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
       <x:c r="I133" s="30"/>
@@ -13579,19 +13614,19 @@
       <x:c r="K133" s="30"/>
       <x:c r="L133" s="30"/>
     </x:row>
-    <x:row r="134" ht="23" customHeight="1">
+    <x:row r="134" ht="15" customHeight="1">
       <x:c r="A134" s="30"/>
-      <x:c r="B134" s="47" t="n">
+      <x:c r="B134" s="63" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C134" s="30"/>
-      <x:c r="D134" s="47" t="n">
+      <x:c r="D134" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E134" s="30"/>
-      <x:c r="F134" s="48"/>
+      <x:c r="F134" s="38"/>
       <x:c r="G134" s="30"/>
-      <x:c r="H134" s="48" t="n">
+      <x:c r="H134" s="36" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I134" s="30"/>
@@ -13599,45 +13634,45 @@
       <x:c r="K134" s="30"/>
       <x:c r="L134" s="30"/>
     </x:row>
-    <x:row r="135" ht="38" customHeight="1">
-      <x:c r="A135" s="45" t="str">
+    <x:row r="135" ht="30" customHeight="1">
+      <x:c r="A135" s="62" t="str">
         <x:v>通信基线 ms</x:v>
       </x:c>
-      <x:c r="B135" s="45" t="str">
+      <x:c r="B135" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="C135" s="45" t="str">
+      <x:c r="C135" s="62" t="str">
         <x:v>通信争用后 ms</x:v>
       </x:c>
-      <x:c r="D135" s="45" t="str">
+      <x:c r="D135" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="E135" s="45" t="str">
+      <x:c r="E135" s="62" t="str">
         <x:v>forward 增量 ms</x:v>
       </x:c>
-      <x:c r="F135" s="45" t="str">
+      <x:c r="F135" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="G135" s="45" t="str">
+      <x:c r="G135" s="62" t="str">
         <x:v>forward 新耗时 ms</x:v>
       </x:c>
-      <x:c r="H135" s="45" t="str">
+      <x:c r="H135" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="I135" s="45" t="str">
+      <x:c r="I135" s="62" t="str">
         <x:v>forward 增幅</x:v>
       </x:c>
-      <x:c r="J135" s="45" t="str">
+      <x:c r="J135" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="K135" s="45" t="str">
+      <x:c r="K135" s="62" t="str">
         <x:v>输入状态</x:v>
       </x:c>
-      <x:c r="L135" s="45" t="str">
+      <x:c r="L135" s="62" t="str">
         <x:v>状态</x:v>
       </x:c>
     </x:row>
-    <x:row r="136" ht="23" customHeight="1">
+    <x:row r="136" ht="15" customHeight="1">
       <x:c r="A136" s="49"/>
       <x:c r="B136" s="49" t="n">
         <x:f>SUM(G140:G161)</x:f>
@@ -13667,7 +13702,7 @@
         <x:v>待填基线</x:v>
       </x:c>
     </x:row>
-    <x:row r="137" ht="23" customHeight="1">
+    <x:row r="137" ht="15" customHeight="1">
       <x:c r="A137" s="30" t="str">
         <x:v>共享比例=0 表示独立链路；暴露系数=0 表示增量完全隐藏。默认均为 1，降幅只作用于带宽项。</x:v>
       </x:c>
@@ -13683,7 +13718,7 @@
       <x:c r="K137" s="30"/>
       <x:c r="L137" s="30"/>
     </x:row>
-    <x:row r="138" ht="23" customHeight="1">
+    <x:row r="138" ht="15" customHeight="1">
       <x:c r="A138" s="30" t="str">
         <x:v>P: AllToAllV + 4 B 计数 Ring；D: A3 BF16 MC2 FullMesh。每事件带宽按端点发送量定义。</x:v>
       </x:c>
@@ -13699,45 +13734,45 @@
       <x:c r="K138" s="30"/>
       <x:c r="L138" s="30"/>
     </x:row>
-    <x:row r="139" ht="38" customHeight="1">
-      <x:c r="A139" s="45" t="str">
+    <x:row r="139" ht="30" customHeight="1">
+      <x:c r="A139" s="62" t="str">
         <x:v>并行域</x:v>
       </x:c>
-      <x:c r="B139" s="45" t="str">
+      <x:c r="B139" s="62" t="str">
         <x:v>模块</x:v>
       </x:c>
-      <x:c r="C139" s="45" t="str">
+      <x:c r="C139" s="62" t="str">
         <x:v>通信事件</x:v>
       </x:c>
-      <x:c r="D139" s="45" t="str">
+      <x:c r="D139" s="62" t="str">
         <x:v>GB/Rank/Step</x:v>
       </x:c>
-      <x:c r="E139" s="45" t="str">
+      <x:c r="E139" s="62" t="str">
         <x:v>有效带宽 GB/s</x:v>
       </x:c>
-      <x:c r="F139" s="45" t="str">
+      <x:c r="F139" s="62" t="str">
         <x:v>共享比例</x:v>
       </x:c>
-      <x:c r="G139" s="45" t="str">
+      <x:c r="G139" s="62" t="str">
         <x:v>基线带宽项 ms</x:v>
       </x:c>
-      <x:c r="H139" s="45" t="str">
+      <x:c r="H139" s="62" t="str">
         <x:v>争用后带宽项 ms</x:v>
       </x:c>
-      <x:c r="I139" s="45" t="str">
+      <x:c r="I139" s="62" t="str">
         <x:v>通信增量 ms</x:v>
       </x:c>
-      <x:c r="J139" s="45" t="str">
+      <x:c r="J139" s="62" t="str">
         <x:v>暴露系数</x:v>
       </x:c>
-      <x:c r="K139" s="45" t="str">
+      <x:c r="K139" s="62" t="str">
         <x:v>forward 增量 ms</x:v>
       </x:c>
-      <x:c r="L139" s="45" t="str">
+      <x:c r="L139" s="62" t="str">
         <x:v>公式口径</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" ht="23" customHeight="1">
+    <x:row r="140" ht="15" customHeight="1">
       <x:c r="A140" s="30" t="str">
         <x:v>Embedding TP</x:v>
       </x:c>
@@ -13751,11 +13786,11 @@
         <x:f>(K107*2^20)/1e9</x:f>
         <x:v>0.025690112</x:v>
       </x:c>
-      <x:c r="E140" s="51" t="n">
+      <x:c r="E140" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F140" s="52" t="n">
+      <x:c r="F140" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G140" s="34" t="n">
@@ -13770,7 +13805,7 @@
         <x:f>G140*F140*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0.028544568888888892</x:v>
       </x:c>
-      <x:c r="J140" s="52" t="n">
+      <x:c r="J140" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K140" s="34" t="n">
@@ -13781,7 +13816,7 @@
         <x:v>原通信行 107</x:v>
       </x:c>
     </x:row>
-    <x:row r="141" ht="23" customHeight="1">
+    <x:row r="141" ht="15" customHeight="1">
       <x:c r="A141" s="30" t="str">
         <x:v>Embedding TP</x:v>
       </x:c>
@@ -13795,11 +13830,11 @@
         <x:f>(K108*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E141" s="51" t="n">
+      <x:c r="E141" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F141" s="52" t="n">
+      <x:c r="F141" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G141" s="34" t="n">
@@ -13814,7 +13849,7 @@
         <x:f>G141*F141*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J141" s="52" t="n">
+      <x:c r="J141" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K141" s="34" t="n">
@@ -13825,7 +13860,7 @@
         <x:v>原通信行 108</x:v>
       </x:c>
     </x:row>
-    <x:row r="142" ht="23" customHeight="1">
+    <x:row r="142" ht="15" customHeight="1">
       <x:c r="A142" s="30" t="str">
         <x:v>Embedding TP</x:v>
       </x:c>
@@ -13839,11 +13874,11 @@
         <x:f>(K109*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E142" s="51" t="n">
+      <x:c r="E142" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F142" s="52" t="n">
+      <x:c r="F142" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G142" s="34" t="n">
@@ -13858,7 +13893,7 @@
         <x:f>G142*F142*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J142" s="52" t="n">
+      <x:c r="J142" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K142" s="34" t="n">
@@ -13869,7 +13904,7 @@
         <x:v>原通信行 109</x:v>
       </x:c>
     </x:row>
-    <x:row r="143" ht="23" customHeight="1">
+    <x:row r="143" ht="15" customHeight="1">
       <x:c r="A143" s="30" t="str">
         <x:v>DSA CP</x:v>
       </x:c>
@@ -13883,11 +13918,11 @@
         <x:f>(K110*2^20)/1e9</x:f>
         <x:v>0.783548416</x:v>
       </x:c>
-      <x:c r="E143" s="51" t="n">
+      <x:c r="E143" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F143" s="52" t="n">
+      <x:c r="F143" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G143" s="34" t="n">
@@ -13902,7 +13937,7 @@
         <x:f>G143*F143*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0.870609351111111</x:v>
       </x:c>
-      <x:c r="J143" s="52" t="n">
+      <x:c r="J143" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K143" s="34" t="n">
@@ -13913,7 +13948,7 @@
         <x:v>原通信行 110</x:v>
       </x:c>
     </x:row>
-    <x:row r="144" ht="23" customHeight="1">
+    <x:row r="144" ht="15" customHeight="1">
       <x:c r="A144" s="30" t="str">
         <x:v>DSA CP</x:v>
       </x:c>
@@ -13927,11 +13962,11 @@
         <x:f>(K111*2^20)/1e9</x:f>
         <x:v>0.895483904</x:v>
       </x:c>
-      <x:c r="E144" s="51" t="n">
+      <x:c r="E144" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F144" s="52" t="n">
+      <x:c r="F144" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G144" s="34" t="n">
@@ -13946,7 +13981,7 @@
         <x:f>G144*F144*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0.9949821155555558</x:v>
       </x:c>
-      <x:c r="J144" s="52" t="n">
+      <x:c r="J144" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K144" s="34" t="n">
@@ -13957,7 +13992,7 @@
         <x:v>原通信行 111</x:v>
       </x:c>
     </x:row>
-    <x:row r="145" ht="23" customHeight="1">
+    <x:row r="145" ht="15" customHeight="1">
       <x:c r="A145" s="30" t="str">
         <x:v>DSA CP</x:v>
       </x:c>
@@ -13971,11 +14006,11 @@
         <x:f>(K112*2^20)/1e9</x:f>
         <x:v>0.11010048</x:v>
       </x:c>
-      <x:c r="E145" s="51" t="n">
+      <x:c r="E145" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F145" s="52" t="n">
+      <x:c r="F145" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G145" s="34" t="n">
@@ -13990,7 +14025,7 @@
         <x:f>G145*F145*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0.12233386666666668</x:v>
       </x:c>
-      <x:c r="J145" s="52" t="n">
+      <x:c r="J145" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K145" s="34" t="n">
@@ -14001,7 +14036,7 @@
         <x:v>原通信行 112</x:v>
       </x:c>
     </x:row>
-    <x:row r="146" ht="23" customHeight="1">
+    <x:row r="146" ht="15" customHeight="1">
       <x:c r="A146" s="30" t="str">
         <x:v>O Proj TP</x:v>
       </x:c>
@@ -14015,11 +14050,11 @@
         <x:f>(K113*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E146" s="51" t="n">
+      <x:c r="E146" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F146" s="52" t="n">
+      <x:c r="F146" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G146" s="34" t="n">
@@ -14034,7 +14069,7 @@
         <x:f>G146*F146*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J146" s="52" t="n">
+      <x:c r="J146" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K146" s="34" t="n">
@@ -14045,7 +14080,7 @@
         <x:v>原通信行 113</x:v>
       </x:c>
     </x:row>
-    <x:row r="147" ht="23" customHeight="1">
+    <x:row r="147" ht="15" customHeight="1">
       <x:c r="A147" s="30" t="str">
         <x:v>EP</x:v>
       </x:c>
@@ -14059,11 +14094,11 @@
         <x:f>(IF(F114=2,E114/7168*H114*(ROUNDUP((ROUNDUP(7168*F114/32,0)*32+32)/480,0)*512),NA()))/1e9</x:f>
         <x:v>0.62963712</x:v>
       </x:c>
-      <x:c r="E147" s="51" t="n">
+      <x:c r="E147" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F147" s="52" t="n">
+      <x:c r="F147" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G147" s="34" t="n">
@@ -14078,7 +14113,7 @@
         <x:f>G147*F147*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0.6995968</x:v>
       </x:c>
-      <x:c r="J147" s="52" t="n">
+      <x:c r="J147" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K147" s="34" t="n">
@@ -14089,7 +14124,7 @@
         <x:v>原通信行 114</x:v>
       </x:c>
     </x:row>
-    <x:row r="148" ht="23" customHeight="1">
+    <x:row r="148" ht="15" customHeight="1">
       <x:c r="A148" s="30" t="str">
         <x:v>EP</x:v>
       </x:c>
@@ -14103,11 +14138,11 @@
         <x:f>(IF(F115=2,K115*2^20+E115/7168*H115*32,NA()))/1e9</x:f>
         <x:v>0.588973056</x:v>
       </x:c>
-      <x:c r="E148" s="51" t="n">
+      <x:c r="E148" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F148" s="52" t="n">
+      <x:c r="F148" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G148" s="34" t="n">
@@ -14122,7 +14157,7 @@
         <x:f>G148*F148*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0.6544145066666667</x:v>
       </x:c>
-      <x:c r="J148" s="52" t="n">
+      <x:c r="J148" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K148" s="34" t="n">
@@ -14133,7 +14168,7 @@
         <x:v>原通信行 115</x:v>
       </x:c>
     </x:row>
-    <x:row r="149" ht="23" customHeight="1">
+    <x:row r="149" ht="15" customHeight="1">
       <x:c r="A149" s="30" t="str">
         <x:v>DP</x:v>
       </x:c>
@@ -14147,11 +14182,11 @@
         <x:f>(K116*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E149" s="51" t="n">
+      <x:c r="E149" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F149" s="52" t="n">
+      <x:c r="F149" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G149" s="34" t="n">
@@ -14166,7 +14201,7 @@
         <x:f>G149*F149*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J149" s="52" t="n">
+      <x:c r="J149" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K149" s="34" t="n">
@@ -14177,7 +14212,7 @@
         <x:v>原通信行 116</x:v>
       </x:c>
     </x:row>
-    <x:row r="150" ht="23" customHeight="1">
+    <x:row r="150" ht="15" customHeight="1">
       <x:c r="A150" s="30" t="str">
         <x:v>DP</x:v>
       </x:c>
@@ -14191,11 +14226,11 @@
         <x:f>(K117*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E150" s="51" t="n">
+      <x:c r="E150" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F150" s="52" t="n">
+      <x:c r="F150" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G150" s="34" t="n">
@@ -14210,7 +14245,7 @@
         <x:f>G150*F150*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J150" s="52" t="n">
+      <x:c r="J150" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K150" s="34" t="n">
@@ -14221,7 +14256,7 @@
         <x:v>原通信行 117</x:v>
       </x:c>
     </x:row>
-    <x:row r="151" ht="23" customHeight="1">
+    <x:row r="151" ht="15" customHeight="1">
       <x:c r="A151" s="30" t="str">
         <x:v>DP</x:v>
       </x:c>
@@ -14235,11 +14270,11 @@
         <x:f>(K118*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E151" s="51" t="n">
+      <x:c r="E151" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F151" s="52" t="n">
+      <x:c r="F151" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G151" s="34" t="n">
@@ -14254,7 +14289,7 @@
         <x:f>G151*F151*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J151" s="52" t="n">
+      <x:c r="J151" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K151" s="34" t="n">
@@ -14265,7 +14300,7 @@
         <x:v>原通信行 118</x:v>
       </x:c>
     </x:row>
-    <x:row r="152" ht="23" customHeight="1">
+    <x:row r="152" ht="15" customHeight="1">
       <x:c r="A152" s="30" t="str">
         <x:v>共享专家 TP</x:v>
       </x:c>
@@ -14279,11 +14314,11 @@
         <x:f>(K119*2^20)/1e9</x:f>
         <x:v>0.783548416</x:v>
       </x:c>
-      <x:c r="E152" s="51" t="n">
+      <x:c r="E152" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F152" s="52" t="n">
+      <x:c r="F152" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G152" s="34" t="n">
@@ -14298,7 +14333,7 @@
         <x:f>G152*F152*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0.870609351111111</x:v>
       </x:c>
-      <x:c r="J152" s="52" t="n">
+      <x:c r="J152" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K152" s="34" t="n">
@@ -14309,7 +14344,7 @@
         <x:v>原通信行 119</x:v>
       </x:c>
     </x:row>
-    <x:row r="153" ht="23" customHeight="1">
+    <x:row r="153" ht="15" customHeight="1">
       <x:c r="A153" s="30" t="str">
         <x:v>共享专家 TP</x:v>
       </x:c>
@@ -14323,11 +14358,11 @@
         <x:f>(K120*2^20)/1e9</x:f>
         <x:v>0.783548416</x:v>
       </x:c>
-      <x:c r="E153" s="51" t="n">
+      <x:c r="E153" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F153" s="52" t="n">
+      <x:c r="F153" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G153" s="34" t="n">
@@ -14342,7 +14377,7 @@
         <x:f>G153*F153*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0.870609351111111</x:v>
       </x:c>
-      <x:c r="J153" s="52" t="n">
+      <x:c r="J153" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K153" s="34" t="n">
@@ -14353,7 +14388,7 @@
         <x:v>原通信行 120</x:v>
       </x:c>
     </x:row>
-    <x:row r="154" ht="23" customHeight="1">
+    <x:row r="154" ht="15" customHeight="1">
       <x:c r="A154" s="30" t="str">
         <x:v>共享专家 TP</x:v>
       </x:c>
@@ -14367,11 +14402,11 @@
         <x:f>(K121*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E154" s="51" t="n">
+      <x:c r="E154" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F154" s="52" t="n">
+      <x:c r="F154" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G154" s="34" t="n">
@@ -14386,7 +14421,7 @@
         <x:f>G154*F154*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J154" s="52" t="n">
+      <x:c r="J154" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K154" s="34" t="n">
@@ -14397,7 +14432,7 @@
         <x:v>原通信行 121</x:v>
       </x:c>
     </x:row>
-    <x:row r="155" ht="23" customHeight="1">
+    <x:row r="155" ht="15" customHeight="1">
       <x:c r="A155" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -14411,11 +14446,11 @@
         <x:f>(K122*2^20)/1e9</x:f>
         <x:v>0.012845056</x:v>
       </x:c>
-      <x:c r="E155" s="51" t="n">
+      <x:c r="E155" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F155" s="52" t="n">
+      <x:c r="F155" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G155" s="34" t="n">
@@ -14430,7 +14465,7 @@
         <x:f>G155*F155*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0.014272284444444446</x:v>
       </x:c>
-      <x:c r="J155" s="52" t="n">
+      <x:c r="J155" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K155" s="34" t="n">
@@ -14441,7 +14476,7 @@
         <x:v>原通信行 122</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" ht="23" customHeight="1">
+    <x:row r="156" ht="15" customHeight="1">
       <x:c r="A156" s="30" t="str">
         <x:v>LM Head TP</x:v>
       </x:c>
@@ -14455,11 +14490,11 @@
         <x:f>(K123*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E156" s="51" t="n">
+      <x:c r="E156" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F156" s="52" t="n">
+      <x:c r="F156" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G156" s="34" t="n">
@@ -14474,7 +14509,7 @@
         <x:f>G156*F156*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J156" s="52" t="n">
+      <x:c r="J156" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K156" s="34" t="n">
@@ -14485,7 +14520,7 @@
         <x:v>原通信行 123</x:v>
       </x:c>
     </x:row>
-    <x:row r="157" ht="23" customHeight="1">
+    <x:row r="157" ht="15" customHeight="1">
       <x:c r="A157" s="30" t="str">
         <x:v>LM Head TP</x:v>
       </x:c>
@@ -14499,11 +14534,11 @@
         <x:f>(K124*2^20)/1e9</x:f>
         <x:v>0.011010048</x:v>
       </x:c>
-      <x:c r="E157" s="51" t="n">
+      <x:c r="E157" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F157" s="52" t="n">
+      <x:c r="F157" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G157" s="34" t="n">
@@ -14518,7 +14553,7 @@
         <x:f>G157*F157*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0.012233386666666669</x:v>
       </x:c>
-      <x:c r="J157" s="52" t="n">
+      <x:c r="J157" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K157" s="34" t="n">
@@ -14529,7 +14564,7 @@
         <x:v>原通信行 124</x:v>
       </x:c>
     </x:row>
-    <x:row r="158" ht="23" customHeight="1">
+    <x:row r="158" ht="15" customHeight="1">
       <x:c r="A158" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -14543,11 +14578,11 @@
         <x:f>(K125*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E158" s="51" t="n">
+      <x:c r="E158" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F158" s="52" t="n">
+      <x:c r="F158" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G158" s="34" t="n">
@@ -14562,7 +14597,7 @@
         <x:f>G158*F158*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J158" s="52" t="n">
+      <x:c r="J158" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K158" s="34" t="n">
@@ -14573,7 +14608,7 @@
         <x:v>原通信行 125</x:v>
       </x:c>
     </x:row>
-    <x:row r="159" ht="23" customHeight="1">
+    <x:row r="159" ht="15" customHeight="1">
       <x:c r="A159" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -14587,11 +14622,11 @@
         <x:f>(K126*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E159" s="51" t="n">
+      <x:c r="E159" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F159" s="52" t="n">
+      <x:c r="F159" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G159" s="34" t="n">
@@ -14606,7 +14641,7 @@
         <x:f>G159*F159*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J159" s="52" t="n">
+      <x:c r="J159" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K159" s="34" t="n">
@@ -14617,7 +14652,7 @@
         <x:v>原通信行 126</x:v>
       </x:c>
     </x:row>
-    <x:row r="160" ht="23" customHeight="1">
+    <x:row r="160" ht="15" customHeight="1">
       <x:c r="A160" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -14631,11 +14666,11 @@
         <x:f>(K127*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E160" s="51" t="n">
+      <x:c r="E160" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F160" s="52" t="n">
+      <x:c r="F160" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G160" s="34" t="n">
@@ -14650,7 +14685,7 @@
         <x:f>G160*F160*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J160" s="52" t="n">
+      <x:c r="J160" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K160" s="34" t="n">
@@ -14661,7 +14696,7 @@
         <x:v>原通信行 127</x:v>
       </x:c>
     </x:row>
-    <x:row r="161" ht="23" customHeight="1">
+    <x:row r="161" ht="15" customHeight="1">
       <x:c r="A161" s="30" t="str">
         <x:v>EP</x:v>
       </x:c>
@@ -14675,11 +14710,11 @@
         <x:f>(IF(E114=0,0,H114*ROUNDUP(384/G114,0)*(G114-1)*32))/1e9</x:f>
         <x:v>0.000655872</x:v>
       </x:c>
-      <x:c r="E161" s="51" t="n">
+      <x:c r="E161" s="64" t="n">
         <x:f>$H$134</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F161" s="52" t="n">
+      <x:c r="F161" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G161" s="34" t="n">
@@ -14694,7 +14729,7 @@
         <x:f>G161*F161*$D$134*$B$134/(1-$B$134)</x:f>
         <x:v>0.0007287466666666667</x:v>
       </x:c>
-      <x:c r="J161" s="52" t="n">
+      <x:c r="J161" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K161" s="34" t="n">
@@ -14705,36 +14740,36 @@
         <x:v>额外控制量</x:v>
       </x:c>
     </x:row>
-    <x:row r="162" ht="23" customHeight="1">
-      <x:c r="A162" s="53" t="str">
+    <x:row r="162" ht="15" customHeight="1">
+      <x:c r="A162" s="40" t="str">
         <x:v>所列事件串行相加</x:v>
       </x:c>
-      <x:c r="B162" s="53"/>
-      <x:c r="C162" s="53"/>
-      <x:c r="D162" s="54" t="n">
+      <x:c r="B162" s="40"/>
+      <x:c r="C162" s="40"/>
+      <x:c r="D162" s="41" t="n">
         <x:f>SUM(D140:D161)</x:f>
         <x:v>4.625040896000001</x:v>
       </x:c>
-      <x:c r="E162" s="54"/>
-      <x:c r="F162" s="53"/>
-      <x:c r="G162" s="54" t="n">
+      <x:c r="E162" s="40"/>
+      <x:c r="F162" s="40"/>
+      <x:c r="G162" s="41" t="n">
         <x:f>SUM(G140:G161)</x:f>
         <x:v>46.250408959999994</x:v>
       </x:c>
-      <x:c r="H162" s="54" t="n">
+      <x:c r="H162" s="41" t="n">
         <x:f>SUM(H140:H161)</x:f>
         <x:v>51.38934328888889</x:v>
       </x:c>
-      <x:c r="I162" s="54" t="n">
+      <x:c r="I162" s="41" t="n">
         <x:f>SUM(I140:I161)</x:f>
         <x:v>5.1389343288888885</x:v>
       </x:c>
-      <x:c r="J162" s="53"/>
-      <x:c r="K162" s="54" t="n">
+      <x:c r="J162" s="40"/>
+      <x:c r="K162" s="41" t="n">
         <x:f>SUM(K140:K161)</x:f>
         <x:v>5.1389343288888885</x:v>
       </x:c>
-      <x:c r="L162" s="53"/>
+      <x:c r="L162" s="40"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="L136:L136">

--- a/models/deepseek-v4-pro-0813/deepseek-v4-pro-0813-analysis.xlsx
+++ b/models/deepseek-v4-pro-0813/deepseek-v4-pro-0813-analysis.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R2b6f6e917e6b4366"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="R0f6fa735acad4fc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分钟场景" sheetId="3" r:id="Reded0bd321904cfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R808b538ff19444ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Rbac5f2fc42374a55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分钟场景" sheetId="3" r:id="Ra1460851042d4549"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -145,7 +145,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="81">
+  <x:cellXfs count="82">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -335,6 +335,9 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -365,7 +368,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -375,7 +378,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -385,7 +388,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -395,7 +398,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -15024,7 +15027,7 @@
       <x:c r="W4" s="30"/>
       <x:c r="X4" s="30"/>
     </x:row>
-    <x:row r="5" ht="22" customHeight="1">
+    <x:row r="5" ht="34" customHeight="1">
       <x:c r="A5" s="30" t="str">
         <x:v>每 P DP 请求数</x:v>
       </x:c>
@@ -15033,16 +15036,18 @@
       </x:c>
       <x:c r="C5" s="30"/>
       <x:c r="D5" s="30"/>
-      <x:c r="E5" s="30" t="str">
-        <x:v>P EP 组数</x:v>
+      <x:c r="E5" s="79" t="str">
+        <x:v>P deployment
+count</x:v>
       </x:c>
       <x:c r="F5" s="66" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="30"/>
       <x:c r="H5" s="30"/>
-      <x:c r="I5" s="30" t="str">
-        <x:v>D EP 组数</x:v>
+      <x:c r="I5" s="79" t="str">
+        <x:v>D deployment
+count</x:v>
       </x:c>
       <x:c r="J5" s="66" t="n">
         <x:v>1</x:v>
@@ -15160,25 +15165,28 @@
       <x:c r="W8" s="30"/>
       <x:c r="X8" s="30"/>
     </x:row>
-    <x:row r="9" ht="22" customHeight="1">
-      <x:c r="A9" s="30" t="str">
-        <x:v>每周期错峰批数</x:v>
+    <x:row r="9" ht="34" customHeight="1">
+      <x:c r="A9" s="79" t="str">
+        <x:v>KV bursts
+per interval</x:v>
       </x:c>
       <x:c r="B9" s="66" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C9" s="30"/>
       <x:c r="D9" s="30"/>
-      <x:c r="E9" s="30" t="str">
-        <x:v>通信共享比例</x:v>
+      <x:c r="E9" s="79" t="str">
+        <x:v>EP shared
+resource fraction</x:v>
       </x:c>
       <x:c r="F9" s="68" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="30"/>
       <x:c r="H9" s="30"/>
-      <x:c r="I9" s="30" t="str">
-        <x:v>关键路径暴露率</x:v>
+      <x:c r="I9" s="79" t="str">
+        <x:v>EP exposed
+comm fraction</x:v>
       </x:c>
       <x:c r="J9" s="68" t="n">
         <x:v>1</x:v>
@@ -15236,9 +15244,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C11" s="30"/>
-      <x:c r="D11" s="30" t="str">
-        <x:v>TTFT 暂作 P 批次间隔；步间隔＝TPOT×平均产出。每周期 1 批表示各 P DP 同步交接。</x:v>
-      </x:c>
+      <x:c r="D11" s="30" t="str"/>
       <x:c r="E11" s="30"/>
       <x:c r="F11" s="30"/>
       <x:c r="G11" s="30"/>
@@ -15261,7 +15267,9 @@
       <x:c r="X11" s="30"/>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="30"/>
+      <x:c r="A12" s="30" t="str">
+        <x:v>P = Prefill，D = Decode。通常只需修改带宽、请求数和 TTFT/TPOT；附加假设可保持默认。</x:v>
+      </x:c>
       <x:c r="B12" s="30"/>
       <x:c r="C12" s="30"/>
       <x:c r="D12" s="30"/>
@@ -15287,7 +15295,9 @@
       <x:c r="X12" s="30"/>
     </x:row>
     <x:row r="13" ht="22" customHeight="1">
-      <x:c r="A13" s="30"/>
+      <x:c r="A13" s="30" t="str">
+        <x:v>Total overhead 表示基线 60 秒工作量的额外耗时；TTFT 在这里作为 KV 批次到达间隔。</x:v>
+      </x:c>
       <x:c r="B13" s="30"/>
       <x:c r="C13" s="30"/>
       <x:c r="D13" s="30"/>
@@ -15366,22 +15376,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G15" s="30"/>
-      <x:c r="H15" s="30" t="str">
-        <x:v>黄色为输入；模型 / EP 带宽可在下表逐项覆盖。</x:v>
-      </x:c>
-      <x:c r="I15" s="30"/>
-      <x:c r="J15" s="30"/>
-      <x:c r="K15" s="30"/>
-      <x:c r="L15" s="30"/>
-      <x:c r="M15" s="30"/>
-      <x:c r="N15" s="30"/>
-      <x:c r="O15" s="30"/>
-      <x:c r="P15" s="30"/>
-      <x:c r="Q15" s="30"/>
-      <x:c r="R15" s="30"/>
-      <x:c r="S15" s="30"/>
-      <x:c r="T15" s="30"/>
-      <x:c r="U15" s="30"/>
+      <x:c r="H15" s="81" t="str">
+        <x:v>Default: P = D = 1; KV bursts = 1; shared / exposed fractions = 100%.</x:v>
+      </x:c>
+      <x:c r="I15" s="81"/>
+      <x:c r="J15" s="81"/>
+      <x:c r="K15" s="81"/>
+      <x:c r="L15" s="81"/>
+      <x:c r="M15" s="81"/>
+      <x:c r="N15" s="81"/>
+      <x:c r="O15" s="81"/>
+      <x:c r="P15" s="81"/>
+      <x:c r="Q15" s="81"/>
+      <x:c r="R15" s="81"/>
+      <x:c r="S15" s="81"/>
+      <x:c r="T15" s="81"/>
+      <x:c r="U15" s="81"/>
       <x:c r="V15" s="30"/>
       <x:c r="W15" s="30"/>
       <x:c r="X15" s="30"/>
@@ -15404,22 +15414,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G16" s="30"/>
-      <x:c r="H16" s="30" t="str">
-        <x:v>时间增量针对基线 60 秒工作量；不表示实测吞吐或 P99。</x:v>
-      </x:c>
-      <x:c r="I16" s="30"/>
-      <x:c r="J16" s="30"/>
-      <x:c r="K16" s="30"/>
-      <x:c r="L16" s="30"/>
-      <x:c r="M16" s="30"/>
-      <x:c r="N16" s="30"/>
-      <x:c r="O16" s="30"/>
-      <x:c r="P16" s="30"/>
-      <x:c r="Q16" s="30"/>
-      <x:c r="R16" s="30"/>
-      <x:c r="S16" s="30"/>
-      <x:c r="T16" s="30"/>
-      <x:c r="U16" s="30"/>
+      <x:c r="H16" s="81" t="str">
+        <x:v>Deployment count：完整 EP 部署的套数；EP32 每套 32 卡，EP256 每套 256 卡。</x:v>
+      </x:c>
+      <x:c r="I16" s="81"/>
+      <x:c r="J16" s="81"/>
+      <x:c r="K16" s="81"/>
+      <x:c r="L16" s="81"/>
+      <x:c r="M16" s="81"/>
+      <x:c r="N16" s="81"/>
+      <x:c r="O16" s="81"/>
+      <x:c r="P16" s="81"/>
+      <x:c r="Q16" s="81"/>
+      <x:c r="R16" s="81"/>
+      <x:c r="S16" s="81"/>
+      <x:c r="T16" s="81"/>
+      <x:c r="U16" s="81"/>
       <x:c r="V16" s="30"/>
       <x:c r="W16" s="30"/>
       <x:c r="X16" s="30"/>
@@ -15442,22 +15452,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G17" s="30"/>
-      <x:c r="H17" s="30" t="str">
-        <x:v>TTFT 只用于到达节奏，本页估算 D 侧 TPOT；P 耗时仍见原表。</x:v>
-      </x:c>
-      <x:c r="I17" s="30"/>
-      <x:c r="J17" s="30"/>
-      <x:c r="K17" s="30"/>
-      <x:c r="L17" s="30"/>
-      <x:c r="M17" s="30"/>
-      <x:c r="N17" s="30"/>
-      <x:c r="O17" s="30"/>
-      <x:c r="P17" s="30"/>
-      <x:c r="Q17" s="30"/>
-      <x:c r="R17" s="30"/>
-      <x:c r="S17" s="30"/>
-      <x:c r="T17" s="30"/>
-      <x:c r="U17" s="30"/>
+      <x:c r="H17" s="81" t="str">
+        <x:v>Shared resource fraction：通信中与 KV 竞争同一资源的比例。100% = 全部；0% = 资源独立。</x:v>
+      </x:c>
+      <x:c r="I17" s="81"/>
+      <x:c r="J17" s="81"/>
+      <x:c r="K17" s="81"/>
+      <x:c r="L17" s="81"/>
+      <x:c r="M17" s="81"/>
+      <x:c r="N17" s="81"/>
+      <x:c r="O17" s="81"/>
+      <x:c r="P17" s="81"/>
+      <x:c r="Q17" s="81"/>
+      <x:c r="R17" s="81"/>
+      <x:c r="S17" s="81"/>
+      <x:c r="T17" s="81"/>
+      <x:c r="U17" s="81"/>
       <x:c r="V17" s="30"/>
       <x:c r="W17" s="30"/>
       <x:c r="X17" s="30"/>
@@ -15474,22 +15484,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="G18" s="30"/>
-      <x:c r="H18" s="30" t="str">
-        <x:v>全 EP＝该步所有等效 EP 通信段都在 KV 窗口内；不代表整步持续时间都重叠。</x:v>
-      </x:c>
-      <x:c r="I18" s="30"/>
-      <x:c r="J18" s="30"/>
-      <x:c r="K18" s="30"/>
-      <x:c r="L18" s="30"/>
-      <x:c r="M18" s="30"/>
-      <x:c r="N18" s="30"/>
-      <x:c r="O18" s="30"/>
-      <x:c r="P18" s="30"/>
-      <x:c r="Q18" s="30"/>
-      <x:c r="R18" s="30"/>
-      <x:c r="S18" s="30"/>
-      <x:c r="T18" s="30"/>
-      <x:c r="U18" s="30"/>
+      <x:c r="H18" s="81" t="str">
+        <x:v>Exposed communication fraction：通信增时最终计入 forward 的比例；被计算遮住的部分不计入。</x:v>
+      </x:c>
+      <x:c r="I18" s="81"/>
+      <x:c r="J18" s="81"/>
+      <x:c r="K18" s="81"/>
+      <x:c r="L18" s="81"/>
+      <x:c r="M18" s="81"/>
+      <x:c r="N18" s="81"/>
+      <x:c r="O18" s="81"/>
+      <x:c r="P18" s="81"/>
+      <x:c r="Q18" s="81"/>
+      <x:c r="R18" s="81"/>
+      <x:c r="S18" s="81"/>
+      <x:c r="T18" s="81"/>
+      <x:c r="U18" s="81"/>
       <x:c r="V18" s="30"/>
       <x:c r="W18" s="30"/>
       <x:c r="X18" s="30"/>
@@ -15502,20 +15512,22 @@
       <x:c r="E19" s="30"/>
       <x:c r="F19" s="30"/>
       <x:c r="G19" s="30"/>
-      <x:c r="H19" s="30"/>
-      <x:c r="I19" s="30"/>
-      <x:c r="J19" s="30"/>
-      <x:c r="K19" s="30"/>
-      <x:c r="L19" s="30"/>
-      <x:c r="M19" s="30"/>
-      <x:c r="N19" s="30"/>
-      <x:c r="O19" s="30"/>
-      <x:c r="P19" s="30"/>
-      <x:c r="Q19" s="30"/>
-      <x:c r="R19" s="30"/>
-      <x:c r="S19" s="30"/>
-      <x:c r="T19" s="30"/>
-      <x:c r="U19" s="30"/>
+      <x:c r="H19" s="81" t="str">
+        <x:v>KV bursts per interval：一批 KV 均分成 m 次、等间隔发送；m = 2 时每次一半，总量不变。</x:v>
+      </x:c>
+      <x:c r="I19" s="81"/>
+      <x:c r="J19" s="81"/>
+      <x:c r="K19" s="81"/>
+      <x:c r="L19" s="81"/>
+      <x:c r="M19" s="81"/>
+      <x:c r="N19" s="81"/>
+      <x:c r="O19" s="81"/>
+      <x:c r="P19" s="81"/>
+      <x:c r="Q19" s="81"/>
+      <x:c r="R19" s="81"/>
+      <x:c r="S19" s="81"/>
+      <x:c r="T19" s="81"/>
+      <x:c r="U19" s="81"/>
       <x:c r="V19" s="30"/>
       <x:c r="W19" s="30"/>
       <x:c r="X19" s="30"/>
@@ -15528,20 +15540,22 @@
       <x:c r="E20" s="30"/>
       <x:c r="F20" s="30"/>
       <x:c r="G20" s="30"/>
-      <x:c r="H20" s="30"/>
-      <x:c r="I20" s="30"/>
-      <x:c r="J20" s="30"/>
-      <x:c r="K20" s="30"/>
-      <x:c r="L20" s="30"/>
-      <x:c r="M20" s="30"/>
-      <x:c r="N20" s="30"/>
-      <x:c r="O20" s="30"/>
-      <x:c r="P20" s="30"/>
-      <x:c r="Q20" s="30"/>
-      <x:c r="R20" s="30"/>
-      <x:c r="S20" s="30"/>
-      <x:c r="T20" s="30"/>
-      <x:c r="U20" s="30"/>
+      <x:c r="H20" s="81" t="str">
+        <x:v>Temporal overlap 由 KV 窗口自动计算；没有 profiling 时，不必另猜 shared / exposed 两个比例。</x:v>
+      </x:c>
+      <x:c r="I20" s="81"/>
+      <x:c r="J20" s="81"/>
+      <x:c r="K20" s="81"/>
+      <x:c r="L20" s="81"/>
+      <x:c r="M20" s="81"/>
+      <x:c r="N20" s="81"/>
+      <x:c r="O20" s="81"/>
+      <x:c r="P20" s="81"/>
+      <x:c r="Q20" s="81"/>
+      <x:c r="R20" s="81"/>
+      <x:c r="S20" s="81"/>
+      <x:c r="T20" s="81"/>
+      <x:c r="U20" s="81"/>
       <x:c r="V20" s="30"/>
       <x:c r="W20" s="30"/>
       <x:c r="X20" s="30"/>
@@ -15609,11 +15623,13 @@
       <x:c r="L22" s="73" t="str">
         <x:v>产出 tokens/步</x:v>
       </x:c>
-      <x:c r="M22" s="73" t="str">
-        <x:v>共享比例</x:v>
-      </x:c>
-      <x:c r="N22" s="73" t="str">
-        <x:v>暴露率</x:v>
+      <x:c r="M22" s="18" t="str">
+        <x:v>EP shared
+resource fraction</x:v>
+      </x:c>
+      <x:c r="N22" s="18" t="str">
+        <x:v>EP exposed
+comm fraction</x:v>
       </x:c>
       <x:c r="O22" s="73" t="str">
         <x:v>配置条件</x:v>
@@ -15892,8 +15908,9 @@
       <x:c r="K29" s="73" t="str">
         <x:v>重叠层调用 次/min</x:v>
       </x:c>
-      <x:c r="L29" s="73" t="str">
-        <x:v>60s 工作增时 ms</x:v>
+      <x:c r="L29" s="18" t="str">
+        <x:v>Total overhead
+ms/60s</x:v>
       </x:c>
       <x:c r="M29" s="73" t="str">
         <x:v>平均 TPOT 增量 μs</x:v>
@@ -17890,8 +17907,9 @@
       <x:c r="U59" s="73" t="str">
         <x:v>基线 FW/min</x:v>
       </x:c>
-      <x:c r="V59" s="73" t="str">
-        <x:v>60s 工作增时 ms</x:v>
+      <x:c r="V59" s="18" t="str">
+        <x:v>Total overhead
+ms/60s</x:v>
       </x:c>
       <x:c r="W59" s="73" t="str">
         <x:v>输入 / 调度状态</x:v>

--- a/models/deepseek-v4-pro-0813/deepseek-v4-pro-0813-analysis.xlsx
+++ b/models/deepseek-v4-pro-0813/deepseek-v4-pro-0813-analysis.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R808b538ff19444ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Rbac5f2fc42374a55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分钟场景" sheetId="3" r:id="Ra1460851042d4549"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="Rc93628a2411349a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="R6b7748c3ec6d4055"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分钟场景" sheetId="3" r:id="R6ad022a570c94956"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,7 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="13">
+  <x:numFmts count="15">
     <x:numFmt numFmtId="200" formatCode="0.##"/>
     <x:numFmt numFmtId="201" formatCode="0.0000"/>
     <x:numFmt numFmtId="202" formatCode="#,##0.####"/>
@@ -29,6 +29,8 @@
     <x:numFmt numFmtId="210" formatCode="#,##0.000"/>
     <x:numFmt numFmtId="211" formatCode="#,##0.000000"/>
     <x:numFmt numFmtId="212" formatCode="0.000000%"/>
+    <x:numFmt numFmtId="213" formatCode="0.00000000%"/>
+    <x:numFmt numFmtId="214" formatCode="[=0]0.000000%;[&lt;0.00000001]&quot;&lt;0.000001%&quot;;0.000000%"/>
   </x:numFmts>
   <x:fonts count="5">
     <x:font>
@@ -58,7 +60,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="13">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -110,6 +112,16 @@
         <x:fgColor rgb="FFD9E2F3"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="3">
     <x:border/>
@@ -145,7 +157,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="82">
+  <x:cellXfs count="90">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -337,6 +349,30 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="213" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="214" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -14909,7 +14945,7 @@
     <x:col min="14" max="14" width="15" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="30" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="21" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="18" hidden="0" customWidth="1"/>
     <x:col min="20" max="20" width="18" hidden="0" customWidth="1"/>
@@ -15924,7 +15960,10 @@
       <x:c r="P29" s="73" t="str">
         <x:v>最低 EP GB/s</x:v>
       </x:c>
-      <x:c r="Q29" s="30"/>
+      <x:c r="Q29" s="88" t="str">
+        <x:v>Decode throughput
+loss (%)</x:v>
+      </x:c>
       <x:c r="R29" s="30"/>
       <x:c r="S29" s="30"/>
       <x:c r="T29" s="30"/>
@@ -15998,7 +16037,10 @@
         <x:f>Q60</x:f>
         <x:v>269.9803392</x:v>
       </x:c>
-      <x:c r="Q30" s="30"/>
+      <x:c r="Q30" s="89" t="n">
+        <x:f>IF(ISNUMBER(L30),L30/(60000+L30),IF(L30="","",L30))</x:f>
+        <x:v>1.213936102836291e-7</x:v>
+      </x:c>
       <x:c r="R30" s="30"/>
       <x:c r="S30" s="30"/>
       <x:c r="T30" s="30"/>
@@ -16072,7 +16114,10 @@
         <x:f>Q61</x:f>
         <x:v>134.9901696</x:v>
       </x:c>
-      <x:c r="Q31" s="30"/>
+      <x:c r="Q31" s="89" t="n">
+        <x:f>IF(ISNUMBER(L31),L31/(60000+L31),IF(L31="","",L31))</x:f>
+        <x:v>6.069680882591694e-8</x:v>
+      </x:c>
       <x:c r="R31" s="30"/>
       <x:c r="S31" s="30"/>
       <x:c r="T31" s="30"/>
@@ -16146,7 +16191,10 @@
         <x:f>Q62</x:f>
         <x:v>67.4950848</x:v>
       </x:c>
-      <x:c r="Q32" s="30"/>
+      <x:c r="Q32" s="89" t="n">
+        <x:f>IF(ISNUMBER(L32),L32/(60000+L32),IF(L32="","",L32))</x:f>
+        <x:v>3.0348405333984146e-8</x:v>
+      </x:c>
       <x:c r="R32" s="30"/>
       <x:c r="S32" s="30"/>
       <x:c r="T32" s="30"/>
@@ -16220,7 +16268,10 @@
         <x:f>Q63</x:f>
         <x:v>44.996723200000005</x:v>
       </x:c>
-      <x:c r="Q33" s="30"/>
+      <x:c r="Q33" s="89" t="n">
+        <x:f>IF(ISNUMBER(L33),L33/(60000+L33),IF(L33="","",L33))</x:f>
+        <x:v>2.0232270427328478e-8</x:v>
+      </x:c>
       <x:c r="R33" s="30"/>
       <x:c r="S33" s="30"/>
       <x:c r="T33" s="30"/>
@@ -16294,7 +16345,10 @@
         <x:f>Q64</x:f>
         <x:v>269.9803392</x:v>
       </x:c>
-      <x:c r="Q34" s="30"/>
+      <x:c r="Q34" s="89" t="n">
+        <x:f>IF(ISNUMBER(L34),L34/(60000+L34),IF(L34="","",L34))</x:f>
+        <x:v>3.091538839342367e-7</x:v>
+      </x:c>
       <x:c r="R34" s="30"/>
       <x:c r="S34" s="30"/>
       <x:c r="T34" s="30"/>
@@ -16368,7 +16422,10 @@
         <x:f>Q65</x:f>
         <x:v>134.9901696</x:v>
       </x:c>
-      <x:c r="Q35" s="30"/>
+      <x:c r="Q35" s="89" t="n">
+        <x:f>IF(ISNUMBER(L35),L35/(60000+L35),IF(L35="","",L35))</x:f>
+        <x:v>1.5457696586115304e-7</x:v>
+      </x:c>
       <x:c r="R35" s="30"/>
       <x:c r="S35" s="30"/>
       <x:c r="T35" s="30"/>
@@ -16442,7 +16499,10 @@
         <x:f>Q66</x:f>
         <x:v>67.4950848</x:v>
       </x:c>
-      <x:c r="Q36" s="30"/>
+      <x:c r="Q36" s="89" t="n">
+        <x:f>IF(ISNUMBER(L36),L36/(60000+L36),IF(L36="","",L36))</x:f>
+        <x:v>7.728848890408657e-8</x:v>
+      </x:c>
       <x:c r="R36" s="30"/>
       <x:c r="S36" s="30"/>
       <x:c r="T36" s="30"/>
@@ -16516,7 +16576,10 @@
         <x:f>Q67</x:f>
         <x:v>44.996723200000005</x:v>
       </x:c>
-      <x:c r="Q37" s="30"/>
+      <x:c r="Q37" s="89" t="n">
+        <x:f>IF(ISNUMBER(L37),L37/(60000+L37),IF(L37="","",L37))</x:f>
+        <x:v>5.1525660596837856e-8</x:v>
+      </x:c>
       <x:c r="R37" s="30"/>
       <x:c r="S37" s="30"/>
       <x:c r="T37" s="30"/>
@@ -16590,7 +16653,10 @@
         <x:f>Q68</x:f>
         <x:v>269.9803392</x:v>
       </x:c>
-      <x:c r="Q38" s="30"/>
+      <x:c r="Q38" s="89" t="n">
+        <x:f>IF(ISNUMBER(L38),L38/(60000+L38),IF(L38="","",L38))</x:f>
+        <x:v>4.0691809906119785e-7</x:v>
+      </x:c>
       <x:c r="R38" s="30"/>
       <x:c r="S38" s="30"/>
       <x:c r="T38" s="30"/>
@@ -16664,7 +16730,10 @@
         <x:f>Q69</x:f>
         <x:v>134.9901696</x:v>
       </x:c>
-      <x:c r="Q39" s="30"/>
+      <x:c r="Q39" s="89" t="n">
+        <x:f>IF(ISNUMBER(L39),L39/(60000+L39),IF(L39="","",L39))</x:f>
+        <x:v>2.0345909092619215e-7</x:v>
+      </x:c>
       <x:c r="R39" s="30"/>
       <x:c r="S39" s="30"/>
       <x:c r="T39" s="30"/>
@@ -16738,7 +16807,10 @@
         <x:f>Q70</x:f>
         <x:v>67.4950848</x:v>
       </x:c>
-      <x:c r="Q40" s="30"/>
+      <x:c r="Q40" s="89" t="n">
+        <x:f>IF(ISNUMBER(L40),L40/(60000+L40),IF(L40="","",L40))</x:f>
+        <x:v>1.0172955581199755e-7</x:v>
+      </x:c>
       <x:c r="R40" s="30"/>
       <x:c r="S40" s="30"/>
       <x:c r="T40" s="30"/>
@@ -16812,7 +16884,10 @@
         <x:f>Q71</x:f>
         <x:v>44.996723200000005</x:v>
       </x:c>
-      <x:c r="Q41" s="30"/>
+      <x:c r="Q41" s="89" t="n">
+        <x:f>IF(ISNUMBER(L41),L41/(60000+L41),IF(L41="","",L41))</x:f>
+        <x:v>6.781970617442124e-8</x:v>
+      </x:c>
       <x:c r="R41" s="30"/>
       <x:c r="S41" s="30"/>
       <x:c r="T41" s="30"/>
@@ -16886,7 +16961,10 @@
         <x:f>Q72</x:f>
         <x:v>277.650528</x:v>
       </x:c>
-      <x:c r="Q42" s="30"/>
+      <x:c r="Q42" s="89" t="n">
+        <x:f>IF(ISNUMBER(L42),L42/(60000+L42),IF(L42="","",L42))</x:f>
+        <x:v>1.2483073166253527e-7</x:v>
+      </x:c>
       <x:c r="R42" s="30"/>
       <x:c r="S42" s="30"/>
       <x:c r="T42" s="30"/>
@@ -16960,7 +17038,10 @@
         <x:f>Q73</x:f>
         <x:v>138.825264</x:v>
       </x:c>
-      <x:c r="Q43" s="30"/>
+      <x:c r="Q43" s="89" t="n">
+        <x:f>IF(ISNUMBER(L43),L43/(60000+L43),IF(L43="","",L43))</x:f>
+        <x:v>6.241536972694577e-8</x:v>
+      </x:c>
       <x:c r="R43" s="30"/>
       <x:c r="S43" s="30"/>
       <x:c r="T43" s="30"/>
@@ -17034,7 +17115,10 @@
         <x:f>Q74</x:f>
         <x:v>69.412632</x:v>
       </x:c>
-      <x:c r="Q44" s="30"/>
+      <x:c r="Q44" s="89" t="n">
+        <x:f>IF(ISNUMBER(L44),L44/(60000+L44),IF(L44="","",L44))</x:f>
+        <x:v>3.1207685837392514e-8</x:v>
+      </x:c>
       <x:c r="R44" s="30"/>
       <x:c r="S44" s="30"/>
       <x:c r="T44" s="30"/>
@@ -17108,7 +17192,10 @@
         <x:f>Q75</x:f>
         <x:v>46.275088</x:v>
       </x:c>
-      <x:c r="Q45" s="30"/>
+      <x:c r="Q45" s="89" t="n">
+        <x:f>IF(ISNUMBER(L45),L45/(60000+L45),IF(L45="","",L45))</x:f>
+        <x:v>2.08051241080216e-8</x:v>
+      </x:c>
       <x:c r="R45" s="30"/>
       <x:c r="S45" s="30"/>
       <x:c r="T45" s="30"/>
@@ -17182,7 +17269,10 @@
         <x:f>Q76</x:f>
         <x:v>277.650528</x:v>
       </x:c>
-      <x:c r="Q46" s="30"/>
+      <x:c r="Q46" s="89" t="n">
+        <x:f>IF(ISNUMBER(L46),L46/(60000+L46),IF(L46="","",L46))</x:f>
+        <x:v>3.179346588298593e-7</x:v>
+      </x:c>
       <x:c r="R46" s="30"/>
       <x:c r="S46" s="30"/>
       <x:c r="T46" s="30"/>
@@ -17256,7 +17346,10 @@
         <x:f>Q77</x:f>
         <x:v>138.825264</x:v>
       </x:c>
-      <x:c r="Q47" s="30"/>
+      <x:c r="Q47" s="89" t="n">
+        <x:f>IF(ISNUMBER(L47),L47/(60000+L47),IF(L47="","",L47))</x:f>
+        <x:v>1.589673546855455e-7</x:v>
+      </x:c>
       <x:c r="R47" s="30"/>
       <x:c r="S47" s="30"/>
       <x:c r="T47" s="30"/>
@@ -17330,7 +17423,10 @@
         <x:f>Q78</x:f>
         <x:v>69.412632</x:v>
       </x:c>
-      <x:c r="Q48" s="30"/>
+      <x:c r="Q48" s="89" t="n">
+        <x:f>IF(ISNUMBER(L48),L48/(60000+L48),IF(L48="","",L48))</x:f>
+        <x:v>7.948368366042821e-8</x:v>
+      </x:c>
       <x:c r="R48" s="30"/>
       <x:c r="S48" s="30"/>
       <x:c r="T48" s="30"/>
@@ -17404,7 +17500,10 @@
         <x:f>Q79</x:f>
         <x:v>46.275088</x:v>
       </x:c>
-      <x:c r="Q49" s="30"/>
+      <x:c r="Q49" s="89" t="n">
+        <x:f>IF(ISNUMBER(L49),L49/(60000+L49),IF(L49="","",L49))</x:f>
+        <x:v>5.2989123844209054e-8</x:v>
+      </x:c>
       <x:c r="R49" s="30"/>
       <x:c r="S49" s="30"/>
       <x:c r="T49" s="30"/>
@@ -17478,7 +17577,10 @@
         <x:f>Q80</x:f>
         <x:v>277.650528</x:v>
       </x:c>
-      <x:c r="Q50" s="30"/>
+      <x:c r="Q50" s="89" t="n">
+        <x:f>IF(ISNUMBER(L50),L50/(60000+L50),IF(L50="","",L50))</x:f>
+        <x:v>4.1847792934110385e-7</x:v>
+      </x:c>
       <x:c r="R50" s="30"/>
       <x:c r="S50" s="30"/>
       <x:c r="T50" s="30"/>
@@ -17552,7 +17654,10 @@
         <x:f>Q81</x:f>
         <x:v>138.825264</x:v>
       </x:c>
-      <x:c r="Q51" s="30"/>
+      <x:c r="Q51" s="89" t="n">
+        <x:f>IF(ISNUMBER(L51),L51/(60000+L51),IF(L51="","",L51))</x:f>
+        <x:v>2.0923900845150542e-7</x:v>
+      </x:c>
       <x:c r="R51" s="30"/>
       <x:c r="S51" s="30"/>
       <x:c r="T51" s="30"/>
@@ -17626,7 +17731,10 @@
         <x:f>Q82</x:f>
         <x:v>69.412632</x:v>
       </x:c>
-      <x:c r="Q52" s="30"/>
+      <x:c r="Q52" s="89" t="n">
+        <x:f>IF(ISNUMBER(L52),L52/(60000+L52),IF(L52="","",L52))</x:f>
+        <x:v>1.0461951517099452e-7</x:v>
+      </x:c>
       <x:c r="R52" s="30"/>
       <x:c r="S52" s="30"/>
       <x:c r="T52" s="30"/>
@@ -17700,7 +17808,10 @@
         <x:f>Q83</x:f>
         <x:v>46.275088</x:v>
       </x:c>
-      <x:c r="Q53" s="30"/>
+      <x:c r="Q53" s="89" t="n">
+        <x:f>IF(ISNUMBER(L53),L53/(60000+L53),IF(L53="","",L53))</x:f>
+        <x:v>6.974634587960599e-8</x:v>
+      </x:c>
       <x:c r="R53" s="30"/>
       <x:c r="S53" s="30"/>
       <x:c r="T53" s="30"/>
@@ -17710,7 +17821,9 @@
       <x:c r="X53" s="30"/>
     </x:row>
     <x:row r="54" ht="22" customHeight="1">
-      <x:c r="A54" s="30"/>
+      <x:c r="A54" s="30" t="str">
+        <x:v>Decode throughput loss = Total overhead / (60000 + Total overhead). Fixed batch size and tokens/step; Decode stays busy.</x:v>
+      </x:c>
       <x:c r="B54" s="30"/>
       <x:c r="C54" s="30"/>
       <x:c r="D54" s="30"/>
